--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{815D8DE8-21B5-48FD-A79A-8BE172C9FB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AAE73B-3E19-4545-A0A1-9BABCB8784BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE6B85FA-6502-4C50-8A39-B9B917ECC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Call Center Relocations Report" sheetId="5" r:id="rId5"/>
     <sheet name="Industry List" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,24 +41,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="318">
-  <si>
-    <t>This worksheet contains 5 sheets. The introductory page, WARN Report Summary, Detailed WARN Report, Call Center Relocations Summary, and Call Center Relocations Report. The second sheet provides an overview of the report according to layoff/closure/relocation types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. The fourth sheet provides an overview of the report specificially for call center relocations. The fifth sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 4 sheets can be found below in cell A3-A6.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="323">
+  <si>
+    <t>County/Parish</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Layoff/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Closure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">No. Of
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Employees</t>
+    </r>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Los Angeles County</t>
+  </si>
+  <si>
+    <t>Layoff Permanent</t>
+  </si>
+  <si>
+    <t>Notice
+Date</t>
+  </si>
+  <si>
+    <t>Effective 
+Date</t>
+  </si>
+  <si>
+    <t>Permanent Layoff</t>
+  </si>
+  <si>
+    <t>Temporary Layoff</t>
+  </si>
+  <si>
+    <t>Not Identified Layoff</t>
+  </si>
+  <si>
+    <t>Permanent Closure</t>
+  </si>
+  <si>
+    <t>Temporary Closure</t>
+  </si>
+  <si>
+    <t>Not Identified Closure</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Report Summary</t>
+  </si>
+  <si>
+    <t>Employees Affected</t>
+  </si>
+  <si>
+    <t>WARN Report Summary</t>
+  </si>
+  <si>
+    <t>Detailed WARN Report</t>
   </si>
   <si>
     <t>WARN Report Index</t>
-  </si>
-  <si>
-    <t>WARN Report Summary</t>
-  </si>
-  <si>
-    <t>Detailed WARN Report</t>
-  </si>
-  <si>
-    <t>Call Center Relocations Summary</t>
-  </si>
-  <si>
-    <t>Call Center Relocations Report</t>
   </si>
   <si>
     <r>
@@ -85,982 +172,14 @@
     </r>
   </si>
   <si>
-    <t>Report Summary</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Employees Affected</t>
-  </si>
-  <si>
-    <t>Permanent Layoff</t>
-  </si>
-  <si>
-    <t>Temporary Layoff</t>
-  </si>
-  <si>
-    <t>Not Identified Layoff</t>
-  </si>
-  <si>
-    <t>Permanent Closure</t>
-  </si>
-  <si>
-    <t>Temporary Closure</t>
-  </si>
-  <si>
-    <t>Not Identified Closure</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WARN REPORT - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07/01/26 to 08/12/2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I128.</t>
-    </r>
-  </si>
-  <si>
-    <t>County/Parish</t>
-  </si>
-  <si>
-    <t>Notice
-Date</t>
-  </si>
-  <si>
     <t>Processed
 Date</t>
   </si>
   <si>
-    <t>Effective 
-Date</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Layoff/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Closure</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">No. Of
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Employees</t>
-    </r>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Related Industry</t>
-  </si>
-  <si>
-    <t>Los Angeles County</t>
-  </si>
-  <si>
-    <t>McDonald's Corporation</t>
-  </si>
-  <si>
-    <t>Closure Permanent</t>
-  </si>
-  <si>
-    <t>17030 Green Drive  City of Industry CA 91745</t>
-  </si>
-  <si>
-    <t>72 Accommodation and Food Services</t>
-  </si>
-  <si>
-    <t>San Mateo County</t>
-  </si>
-  <si>
-    <t>Genentech, Inc.</t>
-  </si>
-  <si>
-    <t>Layoff Permanent</t>
-  </si>
-  <si>
-    <t>1 DNA Way  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>54 Professional Scientific and Technical Services</t>
-  </si>
-  <si>
-    <t>San Bernardino County</t>
-  </si>
-  <si>
-    <t>Athwal FDS Corporation</t>
-  </si>
-  <si>
-    <t>932 West Mill Street  San Bernardino CA 92410</t>
-  </si>
-  <si>
-    <t>56 Administrative and Support and Waste Management and Remediation</t>
-  </si>
-  <si>
-    <t>Sacramento County</t>
-  </si>
-  <si>
-    <t>Blue Diamond Growers</t>
-  </si>
-  <si>
-    <t>1802 C Street  Sacramento CA 95811</t>
-  </si>
-  <si>
-    <t>31-33 Manufacturing</t>
-  </si>
-  <si>
-    <t>Kingdom Animalia, LLC (Hourglass Cosmetics)</t>
-  </si>
-  <si>
-    <t>17110 South Main Street  Carson CA 90248</t>
-  </si>
-  <si>
-    <t>42 Wholesale Trade</t>
-  </si>
-  <si>
-    <t>Orange County</t>
-  </si>
-  <si>
-    <t>DHL Supply Chain</t>
-  </si>
-  <si>
-    <t>701A Sally Pl  Fullerton CA 92831</t>
-  </si>
-  <si>
-    <t>48-49 Transportation and Warehousing</t>
-  </si>
-  <si>
-    <t>Obsidian</t>
-  </si>
-  <si>
-    <t>100 Spectrum Center Dr.  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>71 Arts Entertainment and Recreation</t>
-  </si>
-  <si>
-    <t>Contra Costa County</t>
-  </si>
-  <si>
-    <t>Chevron</t>
-  </si>
-  <si>
-    <t>5001 Executive Parkway, Suite 200  San Ramon CA 94583</t>
-  </si>
-  <si>
-    <t>21 Mining Quarrying Oil and Gas Exraction</t>
-  </si>
-  <si>
-    <t>LeeMAH Electronics</t>
-  </si>
-  <si>
-    <t>155 South Hill Drive  Brisbane CA 94005</t>
-  </si>
-  <si>
-    <t>Alameda County</t>
-  </si>
-  <si>
-    <t>Xpress Delivery LLC (DSJ9)</t>
-  </si>
-  <si>
-    <t>5800 Coliseum Way  Oakland CA 94621</t>
-  </si>
-  <si>
-    <t>San Francisco County</t>
-  </si>
-  <si>
-    <t>OnPoint Logistics LLC</t>
-  </si>
-  <si>
-    <t>749 Toland Street  San Francisco CA 94124</t>
-  </si>
-  <si>
-    <t>Butte County</t>
-  </si>
-  <si>
-    <t>6th Street Center for Youth (Youth for Change)</t>
-  </si>
-  <si>
-    <t>130 W. 6th Street  Chico CA 95928</t>
-  </si>
-  <si>
-    <t>62 Healthcare and Social Assistance</t>
-  </si>
-  <si>
-    <t>Sentinel Restaurant &amp; Hospitality Group LLC</t>
-  </si>
-  <si>
-    <t>627 Sleepy Hollow Ln  Laguna Beach CA 92651</t>
-  </si>
-  <si>
-    <t>The Vons Companies Inc.</t>
-  </si>
-  <si>
-    <t>845 E. California St.  Pasadena CA 91106</t>
-  </si>
-  <si>
-    <t>44-45 Retail Trade</t>
-  </si>
-  <si>
-    <t>GEODIS</t>
-  </si>
-  <si>
-    <t>1950 Palmetto Ave.  Redlands CA 92374</t>
-  </si>
-  <si>
-    <t>Conduent</t>
-  </si>
-  <si>
-    <t>11165 Knott Avenue, Suite D  Cypress CA 90630</t>
-  </si>
-  <si>
-    <t>GMRI, Inc. dba Yard House</t>
-  </si>
-  <si>
-    <t>1875 Newport Blvd., A219  Costa Mesa CA 92627</t>
-  </si>
-  <si>
-    <t>GXO Logistics Worldwide, LLC</t>
-  </si>
-  <si>
-    <t>7010 Cajon Blvd.  San Bernardino CA 92407</t>
-  </si>
-  <si>
-    <t>Udemy, Inc.</t>
-  </si>
-  <si>
-    <t>600 Harrison Street, 3rd Floor  San Francisco CA 94107</t>
-  </si>
-  <si>
-    <t>61 Educational Services</t>
-  </si>
-  <si>
-    <t>Yolo County</t>
-  </si>
-  <si>
-    <t>AWCS, LLC (Cottonwood Post-Acute Rehab</t>
-  </si>
-  <si>
-    <t>Closure Temporary</t>
-  </si>
-  <si>
-    <t>625 Cottonwood St.  Woodland CA 95695</t>
-  </si>
-  <si>
-    <t>Santa Clara County</t>
-  </si>
-  <si>
-    <t>Coursera, Inc.</t>
-  </si>
-  <si>
-    <t>2440West El Camino Real, Suite 500  Mountain View CA 94040</t>
-  </si>
-  <si>
-    <t>ELC Beauty LLC (Too Faced Cosmetics, LLC)</t>
-  </si>
-  <si>
-    <t>18231 W. McDurmott #100  Irvine CA 92614</t>
-  </si>
-  <si>
-    <t>Eargo, Inc.</t>
-  </si>
-  <si>
-    <t>2665 North First Street, Suite 3000  San Jose CA 95134</t>
-  </si>
-  <si>
-    <t>Santa Barbara County</t>
-  </si>
-  <si>
-    <t>Red Lobster Restaurants LLC</t>
-  </si>
-  <si>
-    <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
-  </si>
-  <si>
-    <t>Phillips 66</t>
-  </si>
-  <si>
-    <t>1660 W. Anaheim Street  Wilmington CA 90744</t>
-  </si>
-  <si>
-    <t>NBCUniversal Media, LLC - 1320</t>
-  </si>
-  <si>
-    <t>100 Universal City Plaza, Bldg. 1320  Universal City CA 91608</t>
-  </si>
-  <si>
-    <t>NBCUniversal Media, LLC - 1360</t>
-  </si>
-  <si>
-    <t>100 Universal City Plaza, Bldg. 1360  Universal City CA 91608</t>
-  </si>
-  <si>
-    <t>NBCUniversal Media, LLC -1440</t>
-  </si>
-  <si>
-    <t>100 Universal City Plaza, Bldg. 1440  Universal City CA 91608</t>
-  </si>
-  <si>
-    <t>NBCUniversal Media, LLC - 1460</t>
-  </si>
-  <si>
-    <t>100 Universal City Plaza, Bldg. 1460  Universal City CA 91608</t>
-  </si>
-  <si>
-    <t>Aramark Campus, LLC</t>
-  </si>
-  <si>
-    <t>1259 E Colton Avenue  Redlands CA 92374</t>
-  </si>
-  <si>
-    <t>Monterey Mushrooms, LLC</t>
-  </si>
-  <si>
-    <t>642 Hale Ave.  Morgan Hill CA 95037</t>
-  </si>
-  <si>
-    <t>11 Agriculture Forestry Fishing Hunting</t>
-  </si>
-  <si>
-    <t>Tulare County</t>
-  </si>
-  <si>
-    <t>Ventura Coastal</t>
-  </si>
-  <si>
-    <t>Layoff Temporary</t>
-  </si>
-  <si>
-    <t>531 W. Poplar Avenue  Tipton CA 93272</t>
-  </si>
-  <si>
-    <t>Magic Leap, Inc.</t>
-  </si>
-  <si>
-    <t>1376 Bordeaux Dr.  Sunnyvale CA 94089</t>
-  </si>
-  <si>
-    <t>Wind &amp; Sea Restaurant</t>
-  </si>
-  <si>
-    <t>34699 Golden Lantern  Dana Point CA 92629</t>
-  </si>
-  <si>
-    <t>Solano County</t>
-  </si>
-  <si>
-    <t>DesigneRX Pharmaceuticals, Inc.</t>
-  </si>
-  <si>
-    <t>4941 Allison Parkway, Suite B  Vacaville CA 95688</t>
-  </si>
-  <si>
-    <t>Sonoma County</t>
-  </si>
-  <si>
-    <t>Queen City Staffing</t>
-  </si>
-  <si>
-    <t>2717 Giffen Avenue  Santa Rosa CA 95407</t>
-  </si>
-  <si>
-    <t>New Leaf Community Markets, Inc.</t>
-  </si>
-  <si>
-    <t>5667 Silver Creek Valley Road  San Jose CA 95138</t>
-  </si>
-  <si>
-    <t>Pixar</t>
-  </si>
-  <si>
-    <t>1200 Park Avenue  Emeryville CA 94608</t>
-  </si>
-  <si>
-    <t>CraftForce Services, Inc. (2330 Circadian Way)</t>
-  </si>
-  <si>
-    <t>2330 Circadian Way  Santa Rosa CA 95407</t>
-  </si>
-  <si>
-    <t>CraftForce Services, Inc. (2753 Giffen Avenue)</t>
-  </si>
-  <si>
-    <t>2753 Giffen Avenue  Santa Rosa CA 95407</t>
-  </si>
-  <si>
-    <t>Imperial County</t>
-  </si>
-  <si>
-    <t>Fortrex</t>
-  </si>
-  <si>
-    <t>57 Shank Road  Brawley CA 92227</t>
-  </si>
-  <si>
-    <t>Uber Technologies, Inc. (1655 3rd Street)</t>
-  </si>
-  <si>
-    <t>1655 3rd Street  San Francisco CA 94158</t>
-  </si>
-  <si>
-    <t>Uber Technologies, Inc. (1725 3rd St.)</t>
-  </si>
-  <si>
-    <t>1725 3rd St.  San Francisco CA 94158</t>
-  </si>
-  <si>
-    <t>Uber Technologies, Inc. (Remote)</t>
-  </si>
-  <si>
-    <t>1655 3rd Street (Remote)  San Francisco CA 94158</t>
-  </si>
-  <si>
-    <t>Chick-fil-A &amp; Fig</t>
-  </si>
-  <si>
-    <t>660 S Figueroa St., Ste. 100  Los Angeles CA 90017</t>
-  </si>
-  <si>
-    <t>Monterey County</t>
-  </si>
-  <si>
-    <t>PD Systems</t>
-  </si>
-  <si>
-    <t>Fort Hunter Liggett, Building 3360 Hunter Liggett Road Jolon CA 93928</t>
-  </si>
-  <si>
-    <t>Intel Corporation - Robert Noyce Building</t>
-  </si>
-  <si>
-    <t>2200 Mission College Blvd  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>Intel Corporation - SC-9</t>
-  </si>
-  <si>
-    <t>3601 Juliette Lane  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>Intel Corporation - SC11</t>
-  </si>
-  <si>
-    <t>2191 Laurelwood Rd.  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>Intel Corporation - SC-12</t>
-  </si>
-  <si>
-    <t>3600 Juliette Lane  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>Stanislaus County</t>
-  </si>
-  <si>
-    <t>O'Brien's Market Inc.</t>
-  </si>
-  <si>
-    <t>839 W. Roseburg Avenue  Modesto CA 95350</t>
-  </si>
-  <si>
-    <t>O'Briens Market Inc.</t>
-  </si>
-  <si>
-    <t>4120 Dale Road  Modesto CA 95356</t>
-  </si>
-  <si>
-    <t>Sodexo</t>
-  </si>
-  <si>
-    <t>1020 W Ball Rd.  Anaheim CA 92802</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - San Leandro</t>
-  </si>
-  <si>
-    <t>3041 Teagarden Street  San Leandro CA 94577</t>
-  </si>
-  <si>
-    <t>Kern County</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Bakersfield/Fresno</t>
-  </si>
-  <si>
-    <t>3023 Unicorn Rd.  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC</t>
-  </si>
-  <si>
-    <t>9847 Pioneer Blvd.  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - San Fernando Valley</t>
-  </si>
-  <si>
-    <t>9753 Independence Ave.  Chatsworth CA 91311</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Ana</t>
-  </si>
-  <si>
-    <t>1401 E. Borchard Ave.  Santa Ana CA 92705</t>
-  </si>
-  <si>
-    <t>Riverside County</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Riverside</t>
-  </si>
-  <si>
-    <t>1110 Palmyrita Ave.  Riverside CA 92507</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Sacramento</t>
-  </si>
-  <si>
-    <t>2934 Ramona Ave., Suite 100  Sacramento CA 95826</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - South San Francisco</t>
-  </si>
-  <si>
-    <t>225 Harris Court  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Barbara</t>
-  </si>
-  <si>
-    <t>2373 A Street  Santa Maria CA 93455</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Maria</t>
-  </si>
-  <si>
-    <t>Santa Cruz County</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Cruz</t>
-  </si>
-  <si>
-    <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Petaluma</t>
-  </si>
-  <si>
-    <t>775 Southpoint Blvd.  Petaluma CA 94954</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Rosa</t>
-  </si>
-  <si>
-    <t>1536 Hampton Way, Unit B  Santa Rosa CA 95407</t>
-  </si>
-  <si>
-    <t>ServiceNow, Inc.</t>
-  </si>
-  <si>
-    <t>2225 Lawson Lane  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>San Diego County</t>
-  </si>
-  <si>
-    <t>4801 Eastgate Mall  San Diego CA 92121</t>
-  </si>
-  <si>
-    <t>Silgan Containers</t>
-  </si>
-  <si>
-    <t>430 Doherty Ave.  Modesto CA 95354</t>
-  </si>
-  <si>
-    <t>Tencent America LLC</t>
-  </si>
-  <si>
-    <t>15201 Laguna Canyon Rd.  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>51 Information</t>
-  </si>
-  <si>
-    <t>Federal Express Corporation</t>
-  </si>
-  <si>
-    <t>111 Bird Center Dr  Palm Springs CA 92262</t>
-  </si>
-  <si>
-    <t>12212 Industrial Blvd.  Victorville CA 92395</t>
-  </si>
-  <si>
-    <t>Placer County</t>
-  </si>
-  <si>
-    <t>Sunnyside Restaurant and Lodge</t>
-  </si>
-  <si>
-    <t>1850 West Lake Blvd  Tahoe City CA 96145</t>
-  </si>
-  <si>
-    <t>International Rescue Committee, Inc.</t>
-  </si>
-  <si>
-    <t>2020 Hurley Way, Ste 395  Sacramento CA 95825</t>
-  </si>
-  <si>
-    <t>3446 N. Golden State Blvd, Ste A  Turlock CA 95382</t>
-  </si>
-  <si>
-    <t>WeDriveU, Inc.</t>
-  </si>
-  <si>
-    <t>5438 Victor Street  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>16922 Airport Blvd #25  Mojave CA 93501</t>
-  </si>
-  <si>
-    <t>6075 Lake Isabella Blvd.  Lake Isabella CA 93240</t>
-  </si>
-  <si>
-    <t>1536 Lebec Service Rd.  Lebec CA 92430</t>
-  </si>
-  <si>
-    <t>314 N Hayes St.  Tehachapi CA 93524</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>900 Metro Center Blvd  Foster City CA 94404</t>
-  </si>
-  <si>
-    <t>52 Finance and Insurance</t>
-  </si>
-  <si>
-    <t>Veritone, Inc.</t>
-  </si>
-  <si>
-    <t>5291 California Ave., Ste. 350  Irvine CA 92617</t>
-  </si>
-  <si>
-    <t>Yamaha Motor Finance Corporation U.S.A.</t>
-  </si>
-  <si>
-    <t>6555 Katella Avenue  Cypress CA 90630</t>
-  </si>
-  <si>
-    <t>TPE Acquisition, LLC - 5116</t>
-  </si>
-  <si>
-    <t>5116 Chino Hills Parkway  Chino CA 91710</t>
-  </si>
-  <si>
-    <t>TPE Acquisition, LLC - 5026</t>
-  </si>
-  <si>
-    <t>5026 Chino Hills Parkway  Chino CA 91710</t>
-  </si>
-  <si>
-    <t>Chime Financial, Inc.</t>
-  </si>
-  <si>
-    <t>101 California Street, Suite 500  San Francisco CA 94111</t>
-  </si>
-  <si>
-    <t>San Francisco Pretrial Diversion Project, Inc.</t>
-  </si>
-  <si>
-    <t>1200 Folsom Street  San Francisco CA 94103</t>
-  </si>
-  <si>
-    <t>Nutanix, Inc.</t>
-  </si>
-  <si>
-    <t>1740 Technology Drive  San Jose CA 95110</t>
-  </si>
-  <si>
-    <t>Eclipse Advantage, LLC</t>
-  </si>
-  <si>
-    <t>5540 East 4th Street  Ontario CA 91764</t>
-  </si>
-  <si>
-    <t>Salesforce, Inc.</t>
-  </si>
-  <si>
-    <t>415 Mission Street  San Francisco CA 94105</t>
-  </si>
-  <si>
-    <t>LAZ Parking California (9610 Sky Way)</t>
-  </si>
-  <si>
-    <t>9610 Sky Way  Los Angeles CA 90045</t>
-  </si>
-  <si>
-    <t>81 Other Services Except Public Administration</t>
-  </si>
-  <si>
-    <t>LAZ Parking California (5455 West 111th Street)</t>
-  </si>
-  <si>
-    <t>5455 West 111th Street  Los Angeles CA 90045</t>
-  </si>
-  <si>
-    <t>LAZ Parking California (5251 West 98th Street)</t>
-  </si>
-  <si>
-    <t>5251 West 98th Street  Los Angeles CA 90045</t>
-  </si>
-  <si>
-    <t>Staples Fulfillment Center</t>
-  </si>
-  <si>
-    <t>16501 Trojan Way  La Mirada CA 90638</t>
-  </si>
-  <si>
-    <t>Essendant Co.</t>
-  </si>
-  <si>
-    <t>4555 Redlands Ave.  Perris CA 92571</t>
-  </si>
-  <si>
-    <t>7021 Roseville Rd.  Sacramento CA 95842</t>
-  </si>
-  <si>
-    <t>567 S Riverside Drive  Modesto CA 95354</t>
-  </si>
-  <si>
-    <t>Napa County</t>
-  </si>
-  <si>
-    <t>Renteria Vineyard Management</t>
-  </si>
-  <si>
-    <t>462 Devlin Road  Napa CA 94558</t>
-  </si>
-  <si>
-    <t>G3 Enterprises</t>
-  </si>
-  <si>
-    <t>500 S. Santa Rosa  Modesto CA 95354</t>
-  </si>
-  <si>
-    <t>Bumble Bee Foods, LLC</t>
-  </si>
-  <si>
-    <t>13100 Arctic Circle  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t>1100 Bird Center Drive  Palm Springs CA 92262</t>
-  </si>
-  <si>
-    <t>Sharp Metropolitan Medical Campus  - Sharp Memorial Hospital</t>
-  </si>
-  <si>
-    <t>7901 Frost Street  San Diego CA 92123</t>
-  </si>
-  <si>
-    <t>Sharp Metropolitan Medical Campus - Sharp Mesa Vista</t>
-  </si>
-  <si>
-    <t>Sharp Metropolitan Medical Group - Sharp McDonald Center</t>
-  </si>
-  <si>
-    <t>Sharp Metropolitan Medical Campus - Sharp Mary Birch Hospital</t>
-  </si>
-  <si>
-    <t>Sharp Metropolitan Medical Campus - Sharp Outpatient Pavilion</t>
-  </si>
-  <si>
-    <t>Adventist Health Glendale</t>
-  </si>
-  <si>
-    <t>600 S Central Ave.  Glendale CA 91205</t>
-  </si>
-  <si>
-    <t>EBALDC (100 9th Street)</t>
-  </si>
-  <si>
-    <t>100 9th Street  Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>92 Public Administration</t>
-  </si>
-  <si>
-    <t>EBALDC (121 E 12th Street)</t>
-  </si>
-  <si>
-    <t>121 E 12th Street  Oakland CA 94606</t>
-  </si>
-  <si>
-    <t>EBALDC (1448 10th Street)</t>
-  </si>
-  <si>
-    <t>1448 10th Street 829 East 19th Street Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>EBALDC (1825 San Pablo Ave., Suite 200)</t>
-  </si>
-  <si>
-    <t>1825 San Pablo Ave., Suite 200  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>EBALDC (188 11th Street)</t>
-  </si>
-  <si>
-    <t>188 11th Street  Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>EBALDC (1935 Seminary Ave)</t>
-  </si>
-  <si>
-    <t>1935 Seminary Ave 2530 International BLVD Oakland CA 94621</t>
-  </si>
-  <si>
-    <t>EBALDC (1955 San Pablo Ave)</t>
-  </si>
-  <si>
-    <t>1955 San Pablo Ave  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>EBALDC (2201 Brush St.)</t>
-  </si>
-  <si>
-    <t>2201 Brush St.  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>EBALDC (2555 International BLVD)</t>
-  </si>
-  <si>
-    <t>2555 International BLVD  Oakland CA 94601</t>
-  </si>
-  <si>
-    <t>EBALDC (283 13th Street)</t>
-  </si>
-  <si>
-    <t>283 13th Street  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>EBALDC (2946 International BLVD)</t>
-  </si>
-  <si>
-    <t>2946 International BLVD 2618 East 16th Street Oakland CA 94601</t>
-  </si>
-  <si>
-    <t>EBALDC (3501 San Pablo Ave)</t>
-  </si>
-  <si>
-    <t>3501 San Pablo Ave  Oakland CA 94608</t>
-  </si>
-  <si>
-    <t>EBALDC (3850 San Pablo Ave)</t>
-  </si>
-  <si>
-    <t>3850 San Pablo Ave  Emeryville CA 94608</t>
-  </si>
-  <si>
-    <t>EBALDC (700 Willow Street)</t>
-  </si>
-  <si>
-    <t>700 Willow Street 721 Wood Street Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>EBALDC (801 Pine Street)</t>
-  </si>
-  <si>
-    <t>801 Pine Street  Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>EBALDC (918 Clay Street)</t>
-  </si>
-  <si>
-    <t>918 Clay Street  Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>EBALDC (989 Brush Street)</t>
-  </si>
-  <si>
-    <t>989 Brush Street  Oakland CA 94610</t>
-  </si>
-  <si>
-    <t>EBALDC (120 Macdonald Ave)</t>
-  </si>
-  <si>
-    <t>120 Macdonald Ave 907 Lake Street Richmond CA 94801</t>
-  </si>
-  <si>
-    <t>EBALDC (907 Lake Street)</t>
-  </si>
-  <si>
-    <t>907 Lake Street  San Pablo CA 94806</t>
+    <t>Call Center Relocations Summary</t>
+  </si>
+  <si>
+    <t>Call Center Relocations Report</t>
   </si>
   <si>
     <r>
@@ -1087,6 +206,876 @@
     </r>
   </si>
   <si>
+    <t>American General Life Insurance Company</t>
+  </si>
+  <si>
+    <t>21650 Oxnard Street  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>This worksheet contains 5 sheets. The introductory page, WARN Report Summary, Detailed WARN Report, Call Center Relocations Summary, and Call Center Relocations Report. The second sheet provides an overview of the report according to layoff/closure/relocation types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. The fourth sheet provides an overview of the report specificially for call center relocations. The fifth sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 4 sheets can be found below in cell A3-A6.</t>
+  </si>
+  <si>
+    <t>Related Industry</t>
+  </si>
+  <si>
+    <t>11 Agriculture Forestry Fishing Hunting</t>
+  </si>
+  <si>
+    <t>21 Mining Quarrying Oil and Gas Exraction</t>
+  </si>
+  <si>
+    <t>22 Utilities</t>
+  </si>
+  <si>
+    <t>23 Construction</t>
+  </si>
+  <si>
+    <t>31-33 Manufacturing</t>
+  </si>
+  <si>
+    <t>42 Wholesale Trade</t>
+  </si>
+  <si>
+    <t>44-45 Retail Trade</t>
+  </si>
+  <si>
+    <t>48-49 Transportation and Warehousing</t>
+  </si>
+  <si>
+    <t>51 Information</t>
+  </si>
+  <si>
+    <t>52 Finance and Insurance</t>
+  </si>
+  <si>
+    <t>53 Real Estate and Rental Leasing</t>
+  </si>
+  <si>
+    <t>54 Professional Scientific and Technical Services</t>
+  </si>
+  <si>
+    <t>55 Management of Companies and Enterprises</t>
+  </si>
+  <si>
+    <t>56 Administrative and Support and Waste Management and Remediation</t>
+  </si>
+  <si>
+    <t>61 Educational Services</t>
+  </si>
+  <si>
+    <t>62 Healthcare and Social Assistance</t>
+  </si>
+  <si>
+    <t>71 Arts Entertainment and Recreation</t>
+  </si>
+  <si>
+    <t>72 Accommodation and Food Services</t>
+  </si>
+  <si>
+    <t>81 Other Services Except Public Administration</t>
+  </si>
+  <si>
+    <t>92 Public Administration</t>
+  </si>
+  <si>
+    <t>99 Unclassified</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Closure Permanent</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>San Bernardino County</t>
+  </si>
+  <si>
+    <t>San Mateo County</t>
+  </si>
+  <si>
+    <t>Sacramento County</t>
+  </si>
+  <si>
+    <t>Contra Costa County</t>
+  </si>
+  <si>
+    <t>Genentech, Inc.</t>
+  </si>
+  <si>
+    <t>1 DNA Way  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Chevron</t>
+  </si>
+  <si>
+    <t>5001 Executive Parkway, Suite 200  San Ramon CA 94583</t>
+  </si>
+  <si>
+    <t>Blue Diamond Growers</t>
+  </si>
+  <si>
+    <t>1802 C Street  Sacramento CA 95811</t>
+  </si>
+  <si>
+    <t>DHL Supply Chain</t>
+  </si>
+  <si>
+    <t>McDonald's Corporation</t>
+  </si>
+  <si>
+    <t>17030 Green Drive  City of Industry CA 91745</t>
+  </si>
+  <si>
+    <t>Athwal FDS Corporation</t>
+  </si>
+  <si>
+    <t>932 West Mill Street  San Bernardino CA 92410</t>
+  </si>
+  <si>
+    <t>Kingdom Animalia, LLC (Hourglass Cosmetics)</t>
+  </si>
+  <si>
+    <t>17110 South Main Street  Carson CA 90248</t>
+  </si>
+  <si>
+    <t>701A Sally Pl  Fullerton CA 92831</t>
+  </si>
+  <si>
+    <t>Obsidian</t>
+  </si>
+  <si>
+    <t>100 Spectrum Center Dr.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>LeeMAH Electronics</t>
+  </si>
+  <si>
+    <t>155 South Hill Drive  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>Alameda County</t>
+  </si>
+  <si>
+    <t>Xpress Delivery LLC (DSJ9)</t>
+  </si>
+  <si>
+    <t>5800 Coliseum Way  Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>San Francisco County</t>
+  </si>
+  <si>
+    <t>OnPoint Logistics LLC</t>
+  </si>
+  <si>
+    <t>749 Toland Street  San Francisco CA 94124</t>
+  </si>
+  <si>
+    <t>Butte County</t>
+  </si>
+  <si>
+    <t>6th Street Center for Youth (Youth for Change)</t>
+  </si>
+  <si>
+    <t>130 W. 6th Street  Chico CA 95928</t>
+  </si>
+  <si>
+    <t>Sentinel Restaurant &amp; Hospitality Group LLC</t>
+  </si>
+  <si>
+    <t>627 Sleepy Hollow Ln  Laguna Beach CA 92651</t>
+  </si>
+  <si>
+    <t>The Vons Companies Inc.</t>
+  </si>
+  <si>
+    <t>845 E. California St.  Pasadena CA 91106</t>
+  </si>
+  <si>
+    <t>GEODIS</t>
+  </si>
+  <si>
+    <t>1950 Palmetto Ave.  Redlands CA 92374</t>
+  </si>
+  <si>
+    <t>Conduent</t>
+  </si>
+  <si>
+    <t>11165 Knott Avenue, Suite D  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>GMRI, Inc. dba Yard House</t>
+  </si>
+  <si>
+    <t>1875 Newport Blvd., A219  Costa Mesa CA 92627</t>
+  </si>
+  <si>
+    <t>GXO Logistics Worldwide, LLC</t>
+  </si>
+  <si>
+    <t>7010 Cajon Blvd.  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>Udemy, Inc.</t>
+  </si>
+  <si>
+    <t>600 Harrison Street, 3rd Floor  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Yolo County</t>
+  </si>
+  <si>
+    <t>AWCS, LLC (Cottonwood Post-Acute Rehab</t>
+  </si>
+  <si>
+    <t>Closure Temporary</t>
+  </si>
+  <si>
+    <t>625 Cottonwood St.  Woodland CA 95695</t>
+  </si>
+  <si>
+    <t>Santa Clara County</t>
+  </si>
+  <si>
+    <t>Coursera, Inc.</t>
+  </si>
+  <si>
+    <t>2440West El Camino Real, Suite 500  Mountain View CA 94040</t>
+  </si>
+  <si>
+    <t>ELC Beauty LLC (Too Faced Cosmetics, LLC)</t>
+  </si>
+  <si>
+    <t>18231 W. McDurmott #100  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Eargo, Inc.</t>
+  </si>
+  <si>
+    <t>2665 North First Street, Suite 3000  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Red Lobster Restaurants LLC</t>
+  </si>
+  <si>
+    <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>1660 W. Anaheim Street  Wilmington CA 90744</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1320</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1320  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1360</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1360  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC -1440</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1440  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1460</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1460  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>Aramark Campus, LLC</t>
+  </si>
+  <si>
+    <t>1259 E Colton Avenue  Redlands CA 92374</t>
+  </si>
+  <si>
+    <t>Monterey Mushrooms, LLC</t>
+  </si>
+  <si>
+    <t>642 Hale Ave.  Morgan Hill CA 95037</t>
+  </si>
+  <si>
+    <t>Tulare County</t>
+  </si>
+  <si>
+    <t>Ventura Coastal</t>
+  </si>
+  <si>
+    <t>Layoff Temporary</t>
+  </si>
+  <si>
+    <t>531 W. Poplar Avenue  Tipton CA 93272</t>
+  </si>
+  <si>
+    <t>Magic Leap, Inc.</t>
+  </si>
+  <si>
+    <t>1376 Bordeaux Dr.  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>Wind &amp; Sea Restaurant</t>
+  </si>
+  <si>
+    <t>34699 Golden Lantern  Dana Point CA 92629</t>
+  </si>
+  <si>
+    <t>Solano County</t>
+  </si>
+  <si>
+    <t>DesigneRX Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway, Suite B  Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>Sonoma County</t>
+  </si>
+  <si>
+    <t>Queen City Staffing</t>
+  </si>
+  <si>
+    <t>2717 Giffen Avenue  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>New Leaf Community Markets, Inc.</t>
+  </si>
+  <si>
+    <t>5667 Silver Creek Valley Road  San Jose CA 95138</t>
+  </si>
+  <si>
+    <t>Pixar</t>
+  </si>
+  <si>
+    <t>1200 Park Avenue  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>CraftForce Services, Inc. (2330 Circadian Way)</t>
+  </si>
+  <si>
+    <t>2330 Circadian Way  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>CraftForce Services, Inc. (2753 Giffen Avenue)</t>
+  </si>
+  <si>
+    <t>2753 Giffen Avenue  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>Imperial County</t>
+  </si>
+  <si>
+    <t>Fortrex</t>
+  </si>
+  <si>
+    <t>57 Shank Road  Brawley CA 92227</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (1655 3rd Street)</t>
+  </si>
+  <si>
+    <t>1655 3rd Street  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (1725 3rd St.)</t>
+  </si>
+  <si>
+    <t>1725 3rd St.  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (Remote)</t>
+  </si>
+  <si>
+    <t>1655 3rd Street (Remote)  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Chick-fil-A &amp; Fig</t>
+  </si>
+  <si>
+    <t>660 S Figueroa St., Ste. 100  Los Angeles CA 90017</t>
+  </si>
+  <si>
+    <t>Monterey County</t>
+  </si>
+  <si>
+    <t>PD Systems</t>
+  </si>
+  <si>
+    <t>Fort Hunter Liggett, Building 3360 Hunter Liggett Road Jolon CA 93928</t>
+  </si>
+  <si>
+    <t>Intel Corporation - Robert Noyce Building</t>
+  </si>
+  <si>
+    <t>2200 Mission College Blvd  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC-9</t>
+  </si>
+  <si>
+    <t>3601 Juliette Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC11</t>
+  </si>
+  <si>
+    <t>2191 Laurelwood Rd.  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC-12</t>
+  </si>
+  <si>
+    <t>3600 Juliette Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Stanislaus County</t>
+  </si>
+  <si>
+    <t>O'Brien's Market Inc.</t>
+  </si>
+  <si>
+    <t>839 W. Roseburg Avenue  Modesto CA 95350</t>
+  </si>
+  <si>
+    <t>O'Briens Market Inc.</t>
+  </si>
+  <si>
+    <t>4120 Dale Road  Modesto CA 95356</t>
+  </si>
+  <si>
+    <t>Sodexo</t>
+  </si>
+  <si>
+    <t>1020 W Ball Rd.  Anaheim CA 92802</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Leandro</t>
+  </si>
+  <si>
+    <t>3041 Teagarden Street  San Leandro CA 94577</t>
+  </si>
+  <si>
+    <t>Kern County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Bakersfield/Fresno</t>
+  </si>
+  <si>
+    <t>3023 Unicorn Rd.  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC</t>
+  </si>
+  <si>
+    <t>9847 Pioneer Blvd.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Fernando Valley</t>
+  </si>
+  <si>
+    <t>9753 Independence Ave.  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Ana</t>
+  </si>
+  <si>
+    <t>1401 E. Borchard Ave.  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>Riverside County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Riverside</t>
+  </si>
+  <si>
+    <t>1110 Palmyrita Ave.  Riverside CA 92507</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Sacramento</t>
+  </si>
+  <si>
+    <t>2934 Ramona Ave., Suite 100  Sacramento CA 95826</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - South San Francisco</t>
+  </si>
+  <si>
+    <t>225 Harris Court  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Barbara</t>
+  </si>
+  <si>
+    <t>2373 A Street  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Maria</t>
+  </si>
+  <si>
+    <t>Santa Cruz County</t>
+  </si>
+  <si>
+    <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Petaluma</t>
+  </si>
+  <si>
+    <t>775 Southpoint Blvd.  Petaluma CA 94954</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Rosa</t>
+  </si>
+  <si>
+    <t>1536 Hampton Way, Unit B  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>ServiceNow, Inc.</t>
+  </si>
+  <si>
+    <t>2225 Lawson Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>San Diego County</t>
+  </si>
+  <si>
+    <t>4801 Eastgate Mall  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Silgan Containers</t>
+  </si>
+  <si>
+    <t>430 Doherty Ave.  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Tencent America LLC</t>
+  </si>
+  <si>
+    <t>15201 Laguna Canyon Rd.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>Federal Express Corporation</t>
+  </si>
+  <si>
+    <t>111 Bird Center Dr  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>12212 Industrial Blvd.  Victorville CA 92395</t>
+  </si>
+  <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Sunnyside Restaurant and Lodge</t>
+  </si>
+  <si>
+    <t>1850 West Lake Blvd  Tahoe City CA 96145</t>
+  </si>
+  <si>
+    <t>International Rescue Committee, Inc.</t>
+  </si>
+  <si>
+    <t>2020 Hurley Way, Ste 395  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>3446 N. Golden State Blvd, Ste A  Turlock CA 95382</t>
+  </si>
+  <si>
+    <t>WeDriveU, Inc.</t>
+  </si>
+  <si>
+    <t>5438 Victor Street  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>16922 Airport Blvd #25  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>6075 Lake Isabella Blvd.  Lake Isabella CA 93240</t>
+  </si>
+  <si>
+    <t>1536 Lebec Service Rd.  Lebec CA 92430</t>
+  </si>
+  <si>
+    <t>314 N Hayes St.  Tehachapi CA 93524</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>900 Metro Center Blvd  Foster City CA 94404</t>
+  </si>
+  <si>
+    <t>Veritone, Inc.</t>
+  </si>
+  <si>
+    <t>5291 California Ave., Ste. 350  Irvine CA 92617</t>
+  </si>
+  <si>
+    <t>Yamaha Motor Finance Corporation U.S.A.</t>
+  </si>
+  <si>
+    <t>6555 Katella Avenue  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5116</t>
+  </si>
+  <si>
+    <t>5116 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5026</t>
+  </si>
+  <si>
+    <t>5026 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>Chime Financial, Inc.</t>
+  </si>
+  <si>
+    <t>101 California Street, Suite 500  San Francisco CA 94111</t>
+  </si>
+  <si>
+    <t>1200 Folsom Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Nutanix, Inc.</t>
+  </si>
+  <si>
+    <t>1740 Technology Drive  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Eclipse Advantage, LLC</t>
+  </si>
+  <si>
+    <t>5540 East 4th Street  Ontario CA 91764</t>
+  </si>
+  <si>
+    <t>Salesforce, Inc.</t>
+  </si>
+  <si>
+    <t>415 Mission Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Cruz</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (9610 Sky Way)</t>
+  </si>
+  <si>
+    <t>9610 Sky Way  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (5455 West 111th Street)</t>
+  </si>
+  <si>
+    <t>5455 West 111th Street  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (5251 West 98th Street)</t>
+  </si>
+  <si>
+    <t>5251 West 98th Street  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Staples Fulfillment Center</t>
+  </si>
+  <si>
+    <t>16501 Trojan Way  La Mirada CA 90638</t>
+  </si>
+  <si>
+    <t>Essendant Co.</t>
+  </si>
+  <si>
+    <t>4555 Redlands Ave.  Perris CA 92571</t>
+  </si>
+  <si>
+    <t>7021 Roseville Rd.  Sacramento CA 95842</t>
+  </si>
+  <si>
+    <t>567 S Riverside Drive  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Napa County</t>
+  </si>
+  <si>
+    <t>Renteria Vineyard Management</t>
+  </si>
+  <si>
+    <t>462 Devlin Road  Napa CA 94558</t>
+  </si>
+  <si>
+    <t>G3 Enterprises</t>
+  </si>
+  <si>
+    <t>500 S. Santa Rosa  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>San Francisco Pretrial Diversion Project, Inc.</t>
+  </si>
+  <si>
+    <t>Bumble Bee Foods, LLC</t>
+  </si>
+  <si>
+    <t>13100 Arctic Circle  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t>1100 Bird Center Drive  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus  - Sharp Memorial Hospital</t>
+  </si>
+  <si>
+    <t>7901 Frost Street  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Mesa Vista</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Group - Sharp McDonald Center</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Mary Birch Hospital</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Outpatient Pavilion</t>
+  </si>
+  <si>
+    <t>Adventist Health Glendale</t>
+  </si>
+  <si>
+    <t>600 S Central Ave.  Glendale CA 91205</t>
+  </si>
+  <si>
+    <t>EBALDC (100 9th Street)</t>
+  </si>
+  <si>
+    <t>100 9th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (121 E 12th Street)</t>
+  </si>
+  <si>
+    <t>121 E 12th Street  Oakland CA 94606</t>
+  </si>
+  <si>
+    <t>EBALDC (1448 10th Street)</t>
+  </si>
+  <si>
+    <t>1448 10th Street 829 East 19th Street Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (1825 San Pablo Ave., Suite 200)</t>
+  </si>
+  <si>
+    <t>1825 San Pablo Ave., Suite 200  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (188 11th Street)</t>
+  </si>
+  <si>
+    <t>188 11th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (1935 Seminary Ave)</t>
+  </si>
+  <si>
+    <t>1935 Seminary Ave 2530 International BLVD Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>EBALDC (1955 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>1955 San Pablo Ave  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2201 Brush St.)</t>
+  </si>
+  <si>
+    <t>2201 Brush St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2555 International BLVD)</t>
+  </si>
+  <si>
+    <t>2555 International BLVD  Oakland CA 94601</t>
+  </si>
+  <si>
+    <t>EBALDC (283 13th Street)</t>
+  </si>
+  <si>
+    <t>283 13th Street  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2946 International BLVD)</t>
+  </si>
+  <si>
+    <t>2946 International BLVD 2618 East 16th Street Oakland CA 94601</t>
+  </si>
+  <si>
+    <t>EBALDC (3501 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>3501 San Pablo Ave  Oakland CA 94608</t>
+  </si>
+  <si>
+    <t>EBALDC (3850 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>3850 San Pablo Ave  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>EBALDC (700 Willow Street)</t>
+  </si>
+  <si>
+    <t>700 Willow Street 721 Wood Street Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (801 Pine Street)</t>
+  </si>
+  <si>
+    <t>801 Pine Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (918 Clay Street)</t>
+  </si>
+  <si>
+    <t>918 Clay Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (989 Brush Street)</t>
+  </si>
+  <si>
+    <t>989 Brush Street  Oakland CA 94610</t>
+  </si>
+  <si>
+    <t>EBALDC (120 Macdonald Ave)</t>
+  </si>
+  <si>
+    <t>120 Macdonald Ave 907 Lake Street Richmond CA 94801</t>
+  </si>
+  <si>
+    <t>EBALDC (907 Lake Street)</t>
+  </si>
+  <si>
+    <t>907 Lake Street  San Pablo CA 94806</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1106,7 +1095,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/12/2026
+01/01/2023 - 08/17/2026
 </t>
     </r>
     <r>
@@ -1120,28 +1109,54 @@
     </r>
   </si>
   <si>
-    <t>American General Life Insurance Company</t>
-  </si>
-  <si>
-    <t>21650 Oxnard Street  Woodland Hills CA 91367</t>
-  </si>
-  <si>
-    <t>22 Utilities</t>
-  </si>
-  <si>
-    <t>23 Construction</t>
-  </si>
-  <si>
-    <t>53 Real Estate and Rental Leasing</t>
-  </si>
-  <si>
-    <t>55 Management of Companies and Enterprises</t>
-  </si>
-  <si>
-    <t>99 Unclassified</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>Universal City Studios Productions LLLP</t>
+  </si>
+  <si>
+    <t>Netflix, Inc.</t>
+  </si>
+  <si>
+    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>Roskam Baking Company dba Organic Milling</t>
+  </si>
+  <si>
+    <t>305 South Acacia Street  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WARN REPORT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07/01/26 to 08/17/2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I131.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1154,7 +1169,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="[$-10409]mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1244,6 +1259,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1392,7 +1413,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1469,40 +1490,43 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1830,13 +1854,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="1" tint="0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color theme="1" tint="0.499984740745262"/>
         </top>
@@ -1847,6 +1864,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1918,6 +1942,42 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2185,42 +2245,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
@@ -2283,35 +2307,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A2:B9" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I128" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I128" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I131" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I131" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2331,7 +2355,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{663F80D9-D8E8-4178-A1D5-3F5E9D795F02}" name="DetailedWarnReport5" displayName="DetailedWarnReport5" ref="A2:H3" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{663F80D9-D8E8-4178-A1D5-3F5E9D795F02}" name="DetailedWarnReport5" displayName="DetailedWarnReport5" ref="A2:H3" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A2:H3" xr:uid="{663F80D9-D8E8-4178-A1D5-3F5E9D795F02}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A92120E9-090A-4E03-A02A-363337C6392A}" name="County/Parish" dataDxfId="7"/>
@@ -2348,9 +2372,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2388,7 +2412,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2494,7 +2518,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2636,7 +2660,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2645,39 +2669,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="135">
+    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2694,82 +2718,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="78.75">
+    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>6166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>6354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Not known at this time")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Not known at this time")</f>
@@ -2787,10 +2811,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I128"/>
-  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:I131"/>
+  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
@@ -2806,44 +2830,44 @@
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="102">
+    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75">
+    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B3" s="29">
         <v>46203</v>
@@ -2855,24 +2879,24 @@
         <v>46266</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G3" s="30">
         <v>2</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B4" s="29">
         <v>46199</v>
@@ -2884,24 +2908,24 @@
         <v>46232</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G4" s="30">
         <v>103</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B5" s="29">
         <v>46203</v>
@@ -2913,24 +2937,24 @@
         <v>46264</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G5" s="30">
         <v>35</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B6" s="29">
         <v>46205</v>
@@ -2942,24 +2966,24 @@
         <v>46269</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G6" s="30">
         <v>31</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B7" s="29">
         <v>46205</v>
@@ -2971,24 +2995,24 @@
         <v>46280</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30">
         <v>7</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B8" s="29">
         <v>46205</v>
@@ -3000,24 +3024,24 @@
         <v>46268</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G8" s="30">
         <v>33</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B9" s="29">
         <v>46209</v>
@@ -3029,24 +3053,24 @@
         <v>46269</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G9" s="30">
         <v>52</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" s="29">
         <v>46204</v>
@@ -3058,24 +3082,24 @@
         <v>46266</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G10" s="30">
         <v>180</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B11" s="29">
         <v>46210</v>
@@ -3087,24 +3111,24 @@
         <v>46273</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G11" s="30">
         <v>212</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B12" s="29">
         <v>46212</v>
@@ -3116,24 +3140,24 @@
         <v>46274</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G12" s="30">
         <v>80</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>78</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B13" s="29">
         <v>46212</v>
@@ -3145,24 +3169,24 @@
         <v>46272</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G13" s="30">
         <v>96</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>81</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B14" s="29">
         <v>46213</v>
@@ -3174,24 +3198,24 @@
         <v>46265</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G14" s="30">
         <v>6</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>84</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B15" s="29">
         <v>46211</v>
@@ -3203,24 +3227,24 @@
         <v>46273</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G15" s="30">
         <v>113</v>
       </c>
       <c r="H15" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>86</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B16" s="29">
         <v>46210</v>
@@ -3232,24 +3256,24 @@
         <v>46270</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G16" s="30">
         <v>55</v>
       </c>
       <c r="H16" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>88</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B17" s="29">
         <v>46209</v>
@@ -3261,24 +3285,24 @@
         <v>46268</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G17" s="30">
         <v>81</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>90</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B18" s="29">
         <v>46199</v>
@@ -3290,24 +3314,24 @@
         <v>46262</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G18" s="30">
         <v>51</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>92</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B19" s="29">
         <v>46217</v>
@@ -3319,24 +3343,24 @@
         <v>46279</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G19" s="30">
         <v>78</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>94</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B20" s="29">
         <v>46213</v>
@@ -3348,24 +3372,24 @@
         <v>46283</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G20" s="30">
         <v>46</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>96</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B21" s="29">
         <v>46217</v>
@@ -3377,24 +3401,24 @@
         <v>46276</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G21" s="30">
         <v>28</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>98</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B22" s="29">
         <v>46216</v>
@@ -3406,24 +3430,24 @@
         <v>46276</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G22" s="30">
         <v>158</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>102</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B23" s="29">
         <v>46217</v>
@@ -3435,24 +3459,24 @@
         <v>46276</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G23" s="30">
         <v>31</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>105</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B24" s="29">
         <v>46217</v>
@@ -3464,24 +3488,24 @@
         <v>46295</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G24" s="30">
         <v>67</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>107</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B25" s="29">
         <v>46218</v>
@@ -3493,24 +3517,24 @@
         <v>46279</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G25" s="30">
         <v>57</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>109</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B26" s="29">
         <v>46217</v>
@@ -3522,24 +3546,24 @@
         <v>46265</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G26" s="30">
         <v>37</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>112</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B27" s="29">
         <v>46219</v>
@@ -3551,24 +3575,24 @@
         <v>46281</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G27" s="30">
         <v>5</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>114</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B28" s="29">
         <v>46220</v>
@@ -3580,24 +3604,24 @@
         <v>46262</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G28" s="30">
         <v>3</v>
       </c>
       <c r="H28" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B29" s="29">
         <v>46220</v>
@@ -3609,24 +3633,24 @@
         <v>46262</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G29" s="30">
         <v>5</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="I29" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>118</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B30" s="29">
         <v>46220</v>
@@ -3638,24 +3662,24 @@
         <v>46262</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G30" s="30">
         <v>87</v>
       </c>
       <c r="H30" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>120</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B31" s="29">
         <v>46220</v>
@@ -3667,24 +3691,24 @@
         <v>46262</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G31" s="30">
         <v>55</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="I31" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>122</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B32" s="29">
         <v>46219</v>
@@ -3696,24 +3720,24 @@
         <v>46234</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G32" s="30">
         <v>94</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>124</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B33" s="29">
         <v>46220</v>
@@ -3725,24 +3749,24 @@
         <v>46285</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G33" s="30">
         <v>253</v>
       </c>
       <c r="H33" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="I33" s="31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>126</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B34" s="29">
         <v>46218</v>
@@ -3754,24 +3778,24 @@
         <v>46283</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="G34" s="30">
         <v>71</v>
       </c>
       <c r="H34" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="I34" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>130</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B35" s="29">
         <v>46220</v>
@@ -3783,24 +3807,24 @@
         <v>46296</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G35" s="30">
         <v>76</v>
       </c>
       <c r="H35" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="I35" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>132</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B36" s="29">
         <v>46217</v>
@@ -3812,24 +3836,24 @@
         <v>46280</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G36" s="30">
         <v>198</v>
       </c>
       <c r="H36" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>134</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B37" s="29">
         <v>46223</v>
@@ -3841,24 +3865,24 @@
         <v>46286</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G37" s="30">
         <v>25</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="I37" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>137</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B38" s="29">
         <v>46217</v>
@@ -3870,24 +3894,24 @@
         <v>46278</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G38" s="30">
         <v>49</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>140</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B39" s="29">
         <v>46224</v>
@@ -3899,24 +3923,24 @@
         <v>46285</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G39" s="30">
         <v>61</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>142</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B40" s="29">
         <v>46224</v>
@@ -3928,24 +3952,24 @@
         <v>46291</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G40" s="30">
         <v>108</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>144</v>
+      </c>
+      <c r="I40" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B41" s="29">
         <v>46225</v>
@@ -3957,24 +3981,24 @@
         <v>46285</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G41" s="30">
         <v>51</v>
       </c>
       <c r="H41" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>146</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B42" s="29">
         <v>46225</v>
@@ -3986,372 +4010,372 @@
         <v>46285</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G42" s="30">
         <v>7</v>
       </c>
       <c r="H42" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="B43" s="33">
+        <v>148</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="34">
         <v>46226</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="35">
         <v>46226</v>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="34">
         <v>46255</v>
       </c>
-      <c r="E43" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="36">
+      <c r="E43" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="37">
         <v>91</v>
       </c>
-      <c r="H43" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="I43" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="H43" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="34">
         <v>46225</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>46226</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>46286</v>
       </c>
-      <c r="E44" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G44" s="36">
+      <c r="E44" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="37">
         <v>26</v>
       </c>
-      <c r="H44" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="I44" s="31" t="s">
+      <c r="H44" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="34">
+        <v>46225</v>
+      </c>
+      <c r="C45" s="35">
+        <v>46226</v>
+      </c>
+      <c r="D45" s="34">
+        <v>46286</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="37">
+        <v>1</v>
+      </c>
+      <c r="H45" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="34">
+        <v>46225</v>
+      </c>
+      <c r="C46" s="35">
+        <v>46226</v>
+      </c>
+      <c r="D46" s="34">
+        <v>46286</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="37">
+        <v>14</v>
+      </c>
+      <c r="H46" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C47" s="35">
+        <v>46227</v>
+      </c>
+      <c r="D47" s="34">
+        <v>46292</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="37">
+        <v>77</v>
+      </c>
+      <c r="H47" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="I47" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" s="34">
+        <v>46230</v>
+      </c>
+      <c r="C48" s="34">
+        <v>46230</v>
+      </c>
+      <c r="D48" s="34">
+        <v>46262</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="37">
+        <v>81</v>
+      </c>
+      <c r="H48" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I48" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C49" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D49" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="37">
+        <v>24</v>
+      </c>
+      <c r="H49" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C50" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D50" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="37">
+        <v>10</v>
+      </c>
+      <c r="H50" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="I50" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C51" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D51" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="37">
+        <v>2</v>
+      </c>
+      <c r="H51" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="I51" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C52" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D52" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="37">
+        <v>67</v>
+      </c>
+      <c r="H52" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="34">
+        <v>46230</v>
+      </c>
+      <c r="C53" s="34">
+        <v>46230</v>
+      </c>
+      <c r="D53" s="34">
+        <v>46291</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="37">
         <v>50</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="33">
-        <v>46225</v>
-      </c>
-      <c r="C45" s="34">
-        <v>46226</v>
-      </c>
-      <c r="D45" s="33">
-        <v>46286</v>
-      </c>
-      <c r="E45" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="F45" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="36">
-        <v>1</v>
-      </c>
-      <c r="H45" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="33">
-        <v>46225</v>
-      </c>
-      <c r="C46" s="34">
-        <v>46226</v>
-      </c>
-      <c r="D46" s="33">
-        <v>46286</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="F46" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G46" s="36">
-        <v>14</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I46" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="33">
-        <v>46227</v>
-      </c>
-      <c r="C47" s="34">
-        <v>46227</v>
-      </c>
-      <c r="D47" s="33">
+      <c r="H53" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="I53" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="34">
+        <v>46230</v>
+      </c>
+      <c r="C54" s="34">
+        <v>46230</v>
+      </c>
+      <c r="D54" s="34">
         <v>46292</v>
       </c>
-      <c r="E47" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="F47" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="G47" s="36">
-        <v>77</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="I47" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="33">
-        <v>46230</v>
-      </c>
-      <c r="C48" s="33">
-        <v>46230</v>
-      </c>
-      <c r="D48" s="33">
-        <v>46262</v>
-      </c>
-      <c r="E48" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G48" s="36">
-        <v>81</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="I48" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B49" s="33">
-        <v>46227</v>
-      </c>
-      <c r="C49" s="34">
-        <v>46230</v>
-      </c>
-      <c r="D49" s="33">
-        <v>46249</v>
-      </c>
-      <c r="E49" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G49" s="36">
-        <v>24</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="I49" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B50" s="33">
-        <v>46227</v>
-      </c>
-      <c r="C50" s="34">
-        <v>46230</v>
-      </c>
-      <c r="D50" s="33">
-        <v>46249</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G50" s="36">
-        <v>10</v>
-      </c>
-      <c r="H50" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="I50" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="33">
-        <v>46227</v>
-      </c>
-      <c r="C51" s="34">
-        <v>46230</v>
-      </c>
-      <c r="D51" s="33">
-        <v>46249</v>
-      </c>
-      <c r="E51" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G51" s="36">
-        <v>2</v>
-      </c>
-      <c r="H51" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="I51" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" s="33">
-        <v>46227</v>
-      </c>
-      <c r="C52" s="34">
-        <v>46230</v>
-      </c>
-      <c r="D52" s="33">
-        <v>46249</v>
-      </c>
-      <c r="E52" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="F52" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G52" s="36">
+      <c r="E54" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="37">
         <v>67</v>
       </c>
-      <c r="H52" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="I52" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" s="33">
-        <v>46230</v>
-      </c>
-      <c r="C53" s="33">
-        <v>46230</v>
-      </c>
-      <c r="D53" s="33">
-        <v>46291</v>
-      </c>
-      <c r="E53" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="F53" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="36">
-        <v>50</v>
-      </c>
-      <c r="H53" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="I53" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="33">
-        <v>46230</v>
-      </c>
-      <c r="C54" s="33">
-        <v>46230</v>
-      </c>
-      <c r="D54" s="33">
-        <v>46292</v>
-      </c>
-      <c r="E54" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54" s="36">
-        <v>67</v>
-      </c>
-      <c r="H54" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="I54" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="H54" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B55" s="29">
         <v>46227</v>
@@ -4363,24 +4387,24 @@
         <v>46295</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G55" s="30">
         <v>164</v>
       </c>
       <c r="H55" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="I55" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+        <v>177</v>
+      </c>
+      <c r="I55" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B56" s="29">
         <v>46230</v>
@@ -4392,24 +4416,24 @@
         <v>46266</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G56" s="30">
         <v>4</v>
       </c>
       <c r="H56" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="I56" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>179</v>
+      </c>
+      <c r="I56" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B57" s="29">
         <v>46230</v>
@@ -4421,24 +4445,24 @@
         <v>46266</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G57" s="30">
         <v>1</v>
       </c>
       <c r="H57" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="I57" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>182</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B58" s="29">
         <v>46230</v>
@@ -4450,24 +4474,24 @@
         <v>46266</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G58" s="30">
         <v>6</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="I58" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>184</v>
+      </c>
+      <c r="I58" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B59" s="29">
         <v>46230</v>
@@ -4479,24 +4503,24 @@
         <v>46266</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G59" s="30">
         <v>2</v>
       </c>
       <c r="H59" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="I59" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>186</v>
+      </c>
+      <c r="I59" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B60" s="29">
         <v>46230</v>
@@ -4508,24 +4532,24 @@
         <v>46266</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G60" s="30">
         <v>1</v>
       </c>
       <c r="H60" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="I60" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>188</v>
+      </c>
+      <c r="I60" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B61" s="29">
         <v>46230</v>
@@ -4537,24 +4561,24 @@
         <v>46266</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G61" s="30">
         <v>2</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="I61" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>191</v>
+      </c>
+      <c r="I61" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B62" s="29">
         <v>46230</v>
@@ -4566,24 +4590,24 @@
         <v>46266</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G62" s="30">
         <v>3</v>
       </c>
       <c r="H62" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="I62" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>193</v>
+      </c>
+      <c r="I62" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B63" s="29">
         <v>46230</v>
@@ -4595,24 +4619,24 @@
         <v>46266</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G63" s="30">
         <v>1</v>
       </c>
       <c r="H63" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="I63" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>195</v>
+      </c>
+      <c r="I63" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B64" s="29">
         <v>46230</v>
@@ -4624,24 +4648,24 @@
         <v>46266</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G64" s="30">
         <v>1</v>
       </c>
       <c r="H64" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="I64" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>197</v>
+      </c>
+      <c r="I64" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B65" s="29">
         <v>46230</v>
@@ -4653,24 +4677,24 @@
         <v>46266</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G65" s="30">
         <v>1</v>
       </c>
       <c r="H65" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="I65" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>197</v>
+      </c>
+      <c r="I65" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B66" s="29">
         <v>46230</v>
@@ -4682,24 +4706,24 @@
         <v>46266</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G66" s="30">
         <v>1</v>
       </c>
       <c r="H66" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="I66" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>200</v>
+      </c>
+      <c r="I66" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B67" s="29">
         <v>46230</v>
@@ -4711,24 +4735,24 @@
         <v>46266</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F67" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G67" s="30">
         <v>1</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="I67" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>202</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B68" s="29">
         <v>46230</v>
@@ -4740,24 +4764,24 @@
         <v>46266</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G68" s="30">
         <v>1</v>
       </c>
       <c r="H68" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="I68" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>204</v>
+      </c>
+      <c r="I68" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B69" s="29">
         <v>46231</v>
@@ -4769,24 +4793,24 @@
         <v>46293</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G69" s="30">
         <v>154</v>
       </c>
       <c r="H69" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="I69" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>206</v>
+      </c>
+      <c r="I69" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B70" s="29">
         <v>46231</v>
@@ -4798,24 +4822,24 @@
         <v>46293</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G70" s="30">
         <v>133</v>
       </c>
       <c r="H70" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="I70" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+        <v>208</v>
+      </c>
+      <c r="I70" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B71" s="29">
         <v>46224</v>
@@ -4827,24 +4851,24 @@
         <v>46286</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="G71" s="30">
         <v>55</v>
       </c>
       <c r="H71" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="I71" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>210</v>
+      </c>
+      <c r="I71" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B72" s="29">
         <v>46232</v>
@@ -4856,24 +4880,24 @@
         <v>46293</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G72" s="30">
         <v>68</v>
       </c>
       <c r="H72" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="I72" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>212</v>
+      </c>
+      <c r="I72" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B73" s="29">
         <v>46232</v>
@@ -4885,24 +4909,24 @@
         <v>46294</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G73" s="30">
         <v>62</v>
       </c>
       <c r="H73" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="I73" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>214</v>
+      </c>
+      <c r="I73" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B74" s="29">
         <v>46231</v>
@@ -4914,24 +4938,24 @@
         <v>46293</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G74" s="30">
         <v>54</v>
       </c>
       <c r="H74" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="I74" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>215</v>
+      </c>
+      <c r="I74" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B75" s="29">
         <v>46231</v>
@@ -4943,24 +4967,24 @@
         <v>46299</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G75" s="30">
         <v>47</v>
       </c>
       <c r="H75" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="I75" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>218</v>
+      </c>
+      <c r="I75" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B76" s="29">
         <v>46231</v>
@@ -4972,24 +4996,24 @@
         <v>46295</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G76" s="30">
         <v>41</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="I76" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>220</v>
+      </c>
+      <c r="I76" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B77" s="29">
         <v>46231</v>
@@ -5001,24 +5025,24 @@
         <v>46295</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G77" s="30">
         <v>15</v>
       </c>
       <c r="H77" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="I77" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>221</v>
+      </c>
+      <c r="I77" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B78" s="29">
         <v>46234</v>
@@ -5030,24 +5054,24 @@
         <v>46296</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G78" s="30">
         <v>34</v>
       </c>
       <c r="H78" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="I78" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+        <v>223</v>
+      </c>
+      <c r="I78" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B79" s="29">
         <v>46234</v>
@@ -5059,24 +5083,24 @@
         <v>46296</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G79" s="30">
         <v>12</v>
       </c>
       <c r="H79" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="I79" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>224</v>
+      </c>
+      <c r="I79" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B80" s="29">
         <v>46234</v>
@@ -5088,24 +5112,24 @@
         <v>46296</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F80" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G80" s="30">
         <v>15</v>
       </c>
       <c r="H80" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="I80" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>225</v>
+      </c>
+      <c r="I80" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B81" s="29">
         <v>46234</v>
@@ -5117,24 +5141,24 @@
         <v>46296</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G81" s="30">
         <v>1</v>
       </c>
       <c r="H81" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="I81" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>226</v>
+      </c>
+      <c r="I81" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B82" s="29">
         <v>46234</v>
@@ -5146,24 +5170,24 @@
         <v>46296</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G82" s="30">
         <v>1</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="I82" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>227</v>
+      </c>
+      <c r="I82" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="28" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B83" s="29">
         <v>46234</v>
@@ -5175,24 +5199,24 @@
         <v>46296</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G83" s="30">
         <v>320</v>
       </c>
       <c r="H83" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="I83" s="31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>229</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B84" s="29">
         <v>46233</v>
@@ -5204,24 +5228,24 @@
         <v>46293</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G84" s="30">
         <v>10</v>
       </c>
       <c r="H84" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="I84" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+        <v>231</v>
+      </c>
+      <c r="I84" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B85" s="29">
         <v>46234</v>
@@ -5233,24 +5257,24 @@
         <v>46296</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G85" s="30">
         <v>61</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="I85" s="31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>233</v>
+      </c>
+      <c r="I85" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B86" s="29">
         <v>46234</v>
@@ -5262,24 +5286,24 @@
         <v>46295</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G86" s="30">
         <v>3</v>
       </c>
       <c r="H86" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="I86" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>235</v>
+      </c>
+      <c r="I86" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B87" s="29">
         <v>46234</v>
@@ -5291,24 +5315,24 @@
         <v>46295</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="F87" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G87" s="30">
         <v>12</v>
       </c>
       <c r="H87" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="I87" s="31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>237</v>
+      </c>
+      <c r="I87" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B88" s="29">
         <v>46234</v>
@@ -5320,24 +5344,24 @@
         <v>46295</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G88" s="30">
         <v>135</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="I88" s="31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+        <v>239</v>
+      </c>
+      <c r="I88" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="28" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B89" s="29">
         <v>46233</v>
@@ -5349,24 +5373,24 @@
         <v>46339</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G89" s="30">
         <v>82</v>
       </c>
       <c r="H89" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="I89" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+        <v>240</v>
+      </c>
+      <c r="I89" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B90" s="29">
         <v>46238</v>
@@ -5378,24 +5402,24 @@
         <v>46300</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G90" s="30">
         <v>65</v>
       </c>
       <c r="H90" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="I90" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
+        <v>242</v>
+      </c>
+      <c r="I90" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B91" s="29">
         <v>46239</v>
@@ -5407,24 +5431,24 @@
         <v>46300</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F91" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G91" s="30">
         <v>18</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="I91" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>244</v>
+      </c>
+      <c r="I91" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B92" s="29">
         <v>46239</v>
@@ -5436,285 +5460,285 @@
         <v>46300</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G92" s="30">
         <v>74</v>
       </c>
       <c r="H92" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="I92" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B93" s="37">
+        <v>246</v>
+      </c>
+      <c r="I92" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="38">
         <v>46240</v>
       </c>
-      <c r="C93" s="37">
+      <c r="C93" s="38">
         <v>46240</v>
       </c>
-      <c r="D93" s="37">
+      <c r="D93" s="38">
         <v>46301</v>
       </c>
-      <c r="E93" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="F93" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G93" s="39">
+      <c r="E93" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="F93" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="40">
         <v>139</v>
       </c>
       <c r="H93" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="I93" s="31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B94" s="37">
+        <v>249</v>
+      </c>
+      <c r="I93" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="38">
         <v>46240</v>
       </c>
-      <c r="C94" s="37">
+      <c r="C94" s="38">
         <v>46240</v>
       </c>
-      <c r="D94" s="37">
+      <c r="D94" s="38">
         <v>46301</v>
       </c>
-      <c r="E94" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="F94" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G94" s="39">
+      <c r="E94" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="F94" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="40">
         <v>58</v>
       </c>
       <c r="H94" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="I94" s="31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B95" s="37">
+        <v>251</v>
+      </c>
+      <c r="I94" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="38">
         <v>46240</v>
       </c>
-      <c r="C95" s="37">
+      <c r="C95" s="38">
         <v>46240</v>
       </c>
-      <c r="D95" s="37">
+      <c r="D95" s="38">
         <v>46301</v>
       </c>
-      <c r="E95" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="F95" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G95" s="39">
+      <c r="E95" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="F95" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="40">
         <v>50</v>
       </c>
       <c r="H95" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="I95" s="31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
-      <c r="A96" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B96" s="37">
+        <v>253</v>
+      </c>
+      <c r="I95" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="38">
         <v>46239</v>
       </c>
-      <c r="C96" s="37">
+      <c r="C96" s="38">
         <v>46240</v>
       </c>
-      <c r="D96" s="37">
+      <c r="D96" s="38">
         <v>46304</v>
       </c>
-      <c r="E96" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="F96" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G96" s="39">
+      <c r="E96" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="F96" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G96" s="40">
         <v>109</v>
       </c>
       <c r="H96" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="I96" s="31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="B97" s="37">
+        <v>255</v>
+      </c>
+      <c r="I96" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B97" s="38">
         <v>46237</v>
       </c>
-      <c r="C97" s="37">
+      <c r="C97" s="38">
         <v>46240</v>
       </c>
-      <c r="D97" s="37">
+      <c r="D97" s="38">
         <v>46298</v>
       </c>
-      <c r="E97" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="F97" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G97" s="39">
+      <c r="E97" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="F97" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G97" s="40">
         <v>4</v>
       </c>
       <c r="H97" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="I97" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B98" s="37">
+        <v>257</v>
+      </c>
+      <c r="I97" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B98" s="38">
         <v>46237</v>
       </c>
-      <c r="C98" s="37">
+      <c r="C98" s="38">
         <v>46240</v>
       </c>
-      <c r="D98" s="37">
+      <c r="D98" s="38">
         <v>46298</v>
       </c>
-      <c r="E98" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="F98" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" s="39">
+      <c r="E98" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="F98" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G98" s="40">
         <v>99</v>
       </c>
       <c r="H98" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="I98" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B99" s="37">
+        <v>258</v>
+      </c>
+      <c r="I98" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="38">
         <v>46224</v>
       </c>
-      <c r="C99" s="37">
+      <c r="C99" s="38">
         <v>46240</v>
       </c>
-      <c r="D99" s="37">
+      <c r="D99" s="38">
         <v>46224</v>
       </c>
-      <c r="E99" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="F99" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="G99" s="39">
+      <c r="E99" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="F99" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G99" s="40">
         <v>60</v>
       </c>
       <c r="H99" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="I99" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="B100" s="37">
+        <v>259</v>
+      </c>
+      <c r="I99" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="B100" s="38">
         <v>46241</v>
       </c>
-      <c r="C100" s="37">
+      <c r="C100" s="38">
         <v>46241</v>
       </c>
-      <c r="D100" s="37">
+      <c r="D100" s="38">
         <v>46310</v>
       </c>
-      <c r="E100" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="F100" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="G100" s="39">
+      <c r="E100" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="F100" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G100" s="40">
         <v>91</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="I100" s="31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B101" s="37">
+        <v>262</v>
+      </c>
+      <c r="I100" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" s="38">
         <v>46241</v>
       </c>
-      <c r="C101" s="37">
+      <c r="C101" s="38">
         <v>46244</v>
       </c>
-      <c r="D101" s="37">
+      <c r="D101" s="38">
         <v>46301</v>
       </c>
-      <c r="E101" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="F101" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G101" s="39">
+      <c r="E101" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="40">
         <v>66</v>
       </c>
       <c r="H101" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="I101" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
+        <v>264</v>
+      </c>
+      <c r="I101" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B102" s="29">
         <v>46245</v>
@@ -5726,24 +5750,24 @@
         <v>46345</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G102" s="30">
         <v>197</v>
       </c>
       <c r="H102" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="I102" s="31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+        <v>267</v>
+      </c>
+      <c r="I102" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="28" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B103" s="29">
         <v>46245</v>
@@ -5755,24 +5779,24 @@
         <v>46419</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G103" s="30">
         <v>78</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="I103" s="31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
+        <v>269</v>
+      </c>
+      <c r="I103" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B104" s="29">
         <v>46245</v>
@@ -5784,24 +5808,24 @@
         <v>46305</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G104" s="30">
         <v>20</v>
       </c>
       <c r="H104" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="I104" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+        <v>271</v>
+      </c>
+      <c r="I104" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B105" s="29">
         <v>46245</v>
@@ -5813,24 +5837,24 @@
         <v>46305</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G105" s="30">
         <v>134</v>
       </c>
       <c r="H105" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="I105" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
+        <v>271</v>
+      </c>
+      <c r="I105" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B106" s="29">
         <v>46245</v>
@@ -5842,24 +5866,24 @@
         <v>46305</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G106" s="30">
         <v>2</v>
       </c>
       <c r="H106" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="I106" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
+        <v>271</v>
+      </c>
+      <c r="I106" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B107" s="29">
         <v>46245</v>
@@ -5871,24 +5895,24 @@
         <v>46305</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G107" s="30">
         <v>7</v>
       </c>
       <c r="H107" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="I107" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
+        <v>271</v>
+      </c>
+      <c r="I107" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B108" s="29">
         <v>46245</v>
@@ -5900,24 +5924,24 @@
         <v>46305</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G108" s="30">
         <v>5</v>
       </c>
       <c r="H108" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="I108" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
+        <v>271</v>
+      </c>
+      <c r="I108" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="28" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B109" s="29">
         <v>46245</v>
@@ -5929,24 +5953,24 @@
         <v>46266</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G109" s="30">
         <v>7</v>
       </c>
       <c r="H109" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="I109" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
+        <v>277</v>
+      </c>
+      <c r="I109" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B110" s="29">
         <v>46245</v>
@@ -5958,24 +5982,24 @@
         <v>46305</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G110" s="30">
         <v>4</v>
       </c>
       <c r="H110" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="I110" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
+        <v>279</v>
+      </c>
+      <c r="I110" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B111" s="29">
         <v>46245</v>
@@ -5987,24 +6011,24 @@
         <v>46305</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G111" s="30">
         <v>2</v>
       </c>
       <c r="H111" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="I111" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
+        <v>281</v>
+      </c>
+      <c r="I111" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B112" s="29">
         <v>46245</v>
@@ -6016,24 +6040,24 @@
         <v>46305</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G112" s="30">
         <v>2</v>
       </c>
       <c r="H112" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="I112" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+        <v>283</v>
+      </c>
+      <c r="I112" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B113" s="29">
         <v>46245</v>
@@ -6045,24 +6069,24 @@
         <v>46305</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G113" s="30">
         <v>20</v>
       </c>
       <c r="H113" s="30" t="s">
-        <v>277</v>
-      </c>
-      <c r="I113" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
+        <v>285</v>
+      </c>
+      <c r="I113" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B114" s="29">
         <v>46245</v>
@@ -6074,24 +6098,24 @@
         <v>46305</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G114" s="30">
         <v>4</v>
       </c>
       <c r="H114" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="I114" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
+        <v>287</v>
+      </c>
+      <c r="I114" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B115" s="29">
         <v>46245</v>
@@ -6103,24 +6127,24 @@
         <v>46305</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G115" s="30">
         <v>2</v>
       </c>
       <c r="H115" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="I115" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9">
+        <v>289</v>
+      </c>
+      <c r="I115" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B116" s="29">
         <v>46245</v>
@@ -6132,24 +6156,24 @@
         <v>46305</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F116" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G116" s="30">
         <v>9</v>
       </c>
       <c r="H116" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="I116" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9">
+        <v>291</v>
+      </c>
+      <c r="I116" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B117" s="29">
         <v>46245</v>
@@ -6161,24 +6185,24 @@
         <v>46305</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F117" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G117" s="30">
         <v>5</v>
       </c>
       <c r="H117" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="I117" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9">
+        <v>293</v>
+      </c>
+      <c r="I117" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B118" s="29">
         <v>46245</v>
@@ -6190,24 +6214,24 @@
         <v>46305</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G118" s="30">
         <v>5</v>
       </c>
       <c r="H118" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="I118" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
+        <v>295</v>
+      </c>
+      <c r="I118" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B119" s="29">
         <v>46245</v>
@@ -6219,24 +6243,24 @@
         <v>46305</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G119" s="30">
         <v>4</v>
       </c>
       <c r="H119" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="I119" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9">
+        <v>297</v>
+      </c>
+      <c r="I119" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B120" s="29">
         <v>46245</v>
@@ -6248,24 +6272,24 @@
         <v>46305</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G120" s="30">
         <v>2</v>
       </c>
       <c r="H120" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="I120" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9">
+        <v>299</v>
+      </c>
+      <c r="I120" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B121" s="29">
         <v>46245</v>
@@ -6277,24 +6301,24 @@
         <v>46305</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G121" s="30">
         <v>9</v>
       </c>
       <c r="H121" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="I121" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9">
+        <v>301</v>
+      </c>
+      <c r="I121" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B122" s="29">
         <v>46245</v>
@@ -6306,24 +6330,24 @@
         <v>46305</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G122" s="30">
         <v>1</v>
       </c>
       <c r="H122" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="I122" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
+        <v>303</v>
+      </c>
+      <c r="I122" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B123" s="29">
         <v>46245</v>
@@ -6335,24 +6359,24 @@
         <v>46305</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G123" s="30">
         <v>2</v>
       </c>
       <c r="H123" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="I123" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
+        <v>305</v>
+      </c>
+      <c r="I123" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B124" s="29">
         <v>46245</v>
@@ -6364,24 +6388,24 @@
         <v>46305</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G124" s="30">
         <v>4</v>
       </c>
       <c r="H124" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="I124" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9">
+        <v>307</v>
+      </c>
+      <c r="I124" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B125" s="29">
         <v>46245</v>
@@ -6393,24 +6417,24 @@
         <v>46305</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G125" s="30">
         <v>2</v>
       </c>
       <c r="H125" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="I125" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
+        <v>309</v>
+      </c>
+      <c r="I125" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B126" s="29">
         <v>46245</v>
@@ -6422,24 +6446,24 @@
         <v>46305</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G126" s="30">
         <v>2</v>
       </c>
       <c r="H126" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="I126" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9">
+        <v>311</v>
+      </c>
+      <c r="I126" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B127" s="29">
         <v>46245</v>
@@ -6451,24 +6475,24 @@
         <v>46305</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G127" s="30">
         <v>1</v>
       </c>
       <c r="H127" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="I127" s="31" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+        <v>313</v>
+      </c>
+      <c r="I127" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B128" s="29">
         <v>46245</v>
@@ -6480,19 +6504,106 @@
         <v>46305</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F128" s="28" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G128" s="30">
         <v>2</v>
       </c>
       <c r="H128" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="I128" s="31" t="s">
-        <v>271</v>
+        <v>315</v>
+      </c>
+      <c r="I128" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" s="29">
+        <v>46247</v>
+      </c>
+      <c r="C129" s="29">
+        <v>46247</v>
+      </c>
+      <c r="D129" s="29">
+        <v>46308</v>
+      </c>
+      <c r="E129" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F129" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" s="30">
+        <v>14</v>
+      </c>
+      <c r="H129" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I129" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" s="29">
+        <v>46247</v>
+      </c>
+      <c r="C130" s="29">
+        <v>46248</v>
+      </c>
+      <c r="D130" s="29">
+        <v>46217</v>
+      </c>
+      <c r="E130" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="F130" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="30">
+        <v>59</v>
+      </c>
+      <c r="H130" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="I130" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C131" s="29">
+        <v>46251</v>
+      </c>
+      <c r="D131" s="29">
+        <v>46297</v>
+      </c>
+      <c r="E131" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="F131" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="30">
+        <v>115</v>
+      </c>
+      <c r="H131" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="I131" s="32" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -6509,7 +6620,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I128</xm:sqref>
+          <xm:sqref>I3:I131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6520,82 +6631,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="97.5">
+    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" s="24">
         <f>SUM('Call Center Relocations Report'!G:G)</f>
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Layoff Permanent")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Layoff Temporary")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Layoff Not Identified")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Closure Permanent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Closure Temporary")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="24">
         <f>COUNTIF('Call Center Relocations Report'!F:F,"Closure Not Identified")</f>
@@ -6616,7 +6727,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
@@ -6628,41 +6739,41 @@
     <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99.75">
+    <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24.75">
+    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B3" s="9">
         <v>44984</v>
@@ -6674,16 +6785,16 @@
         <v>45047</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>310</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G3" s="6">
         <v>163</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>311</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -6697,119 +6808,119 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -7025,6 +7136,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
@@ -7035,29 +7155,52 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760B78E6-4CA6-4F80-86E0-53400489F8D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D160E30-BC30-4B6D-ACC5-72FBA8F9F1F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{278F0559-74F3-4D76-B75C-EA9EBA777461}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C46929A-3DE1-4C62-9238-C2B188611275}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90BD3F23-18DF-4AC3-9449-DAE38248BE25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD289F2-34C9-4527-98E3-ED4CBE06E698}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE6B85FA-6502-4C50-8A39-B9B917ECC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{029449D0-7F52-41A2-A4A2-F7EDFCBB33B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="337">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1076,6 +1076,21 @@
     <t>907 Lake Street  San Pablo CA 94806</t>
   </si>
   <si>
+    <t>Universal City Studios Productions LLLP</t>
+  </si>
+  <si>
+    <t>Netflix, Inc.</t>
+  </si>
+  <si>
+    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>Roskam Baking Company dba Organic Milling</t>
+  </si>
+  <si>
+    <t>305 South Acacia Street  San Dimas CA 91773</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1095,7 +1110,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/17/2026
+01/01/2023 - 08/19/2026
 </t>
     </r>
     <r>
@@ -1109,19 +1124,46 @@
     </r>
   </si>
   <si>
-    <t>Universal City Studios Productions LLLP</t>
-  </si>
-  <si>
-    <t>Netflix, Inc.</t>
-  </si>
-  <si>
-    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
-  </si>
-  <si>
-    <t>Roskam Baking Company dba Organic Milling</t>
-  </si>
-  <si>
-    <t>305 South Acacia Street  San Dimas CA 91773</t>
+    <t>Corteva Agriscience LLC</t>
+  </si>
+  <si>
+    <t>901 Loveridge Road  Pittsburg CA 94565</t>
+  </si>
+  <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Stockton Truss LLC</t>
+  </si>
+  <si>
+    <t>4408 E Fremont St  Stockton CA 95215</t>
+  </si>
+  <si>
+    <t>Ventura County</t>
+  </si>
+  <si>
+    <t>Volume Services, Inc. (Sodexo)</t>
+  </si>
+  <si>
+    <t>40 Presidential Drive  Simi Valley CA 93065</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Executive Place</t>
+  </si>
+  <si>
+    <t>2865 Executive Place  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Harmony Grove</t>
+  </si>
+  <si>
+    <t>2005 Harmony Grove Rd.  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing CO., LLC - Citracado Parkway</t>
+  </si>
+  <si>
+    <t>1999 Citracado Parkway  Escondido CA 92029</t>
   </si>
   <si>
     <r>
@@ -1135,7 +1177,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/17/2026</t>
+      <t>07/01/26 to 08/19/2026</t>
     </r>
     <r>
       <rPr>
@@ -1155,7 +1197,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I131.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I138.</t>
     </r>
   </si>
 </sst>
@@ -2321,8 +2363,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I131" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I131" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I138" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I138" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2743,7 +2785,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>6354</v>
+        <v>6777</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2752,7 +2794,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2779,7 +2821,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2811,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -2832,7 +2874,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -6533,7 +6575,7 @@
         <v>46308</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F129" s="28" t="s">
         <v>6</v>
@@ -6562,7 +6604,7 @@
         <v>46217</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F130" s="28" t="s">
         <v>6</v>
@@ -6571,7 +6613,7 @@
         <v>59</v>
       </c>
       <c r="H130" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I130" s="32" t="s">
         <v>38</v>
@@ -6591,7 +6633,7 @@
         <v>46297</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F131" s="28" t="s">
         <v>6</v>
@@ -6600,9 +6642,212 @@
         <v>115</v>
       </c>
       <c r="H131" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I131" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B132" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C132" s="29">
+        <v>46251</v>
+      </c>
+      <c r="D132" s="29">
+        <v>46311</v>
+      </c>
+      <c r="E132" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F132" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="30">
+        <v>205</v>
+      </c>
+      <c r="H132" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C133" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D133" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E133" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="F133" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="30">
+        <v>2</v>
+      </c>
+      <c r="H133" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="I133" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="B134" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C134" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D134" s="29">
+        <v>46313</v>
+      </c>
+      <c r="E134" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="F134" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="30">
+        <v>65</v>
+      </c>
+      <c r="H134" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="I134" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="B135" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C135" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D135" s="29">
+        <v>46311</v>
+      </c>
+      <c r="E135" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="F135" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" s="30">
+        <v>93</v>
+      </c>
+      <c r="H135" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="I135" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B136" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C136" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D136" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="F136" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G136" s="30">
+        <v>6</v>
+      </c>
+      <c r="H136" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="I136" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B137" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C137" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D137" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E137" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="F137" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G137" s="30">
+        <v>2</v>
+      </c>
+      <c r="H137" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="I137" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B138" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C138" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D138" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="F138" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G138" s="30">
+        <v>50</v>
+      </c>
+      <c r="H138" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="I138" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6620,7 +6865,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I131</xm:sqref>
+          <xm:sqref>I3:I138</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6741,7 +6986,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E1"/>
     </row>
@@ -7156,7 +7401,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D160E30-BC30-4B6D-ACC5-72FBA8F9F1F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{500E637C-873A-43B6-8715-BFB319569621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7175,7 +7420,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C46929A-3DE1-4C62-9238-C2B188611275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FEEF22E-DAEA-47B0-88B1-91EB0D24CA24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -7183,18 +7428,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD289F2-34C9-4527-98E3-ED4CBE06E698}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F711838-DD4B-4223-BB8C-8018EF2910A0}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{029449D0-7F52-41A2-A4A2-F7EDFCBB33B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C3697B-36EF-4E1D-816F-E31B4510F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="367">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1091,6 +1091,48 @@
     <t>305 South Acacia Street  San Dimas CA 91773</t>
   </si>
   <si>
+    <t>Corteva Agriscience LLC</t>
+  </si>
+  <si>
+    <t>901 Loveridge Road  Pittsburg CA 94565</t>
+  </si>
+  <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Stockton Truss LLC</t>
+  </si>
+  <si>
+    <t>4408 E Fremont St  Stockton CA 95215</t>
+  </si>
+  <si>
+    <t>Ventura County</t>
+  </si>
+  <si>
+    <t>Volume Services, Inc. (Sodexo)</t>
+  </si>
+  <si>
+    <t>40 Presidential Drive  Simi Valley CA 93065</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Executive Place</t>
+  </si>
+  <si>
+    <t>2865 Executive Place  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Harmony Grove</t>
+  </si>
+  <si>
+    <t>2005 Harmony Grove Rd.  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing CO., LLC - Citracado Parkway</t>
+  </si>
+  <si>
+    <t>1999 Citracado Parkway  Escondido CA 92029</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1110,7 +1152,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/19/2026
+01/01/2023 - 08/24/2026
 </t>
     </r>
     <r>
@@ -1124,46 +1166,94 @@
     </r>
   </si>
   <si>
-    <t>Corteva Agriscience LLC</t>
-  </si>
-  <si>
-    <t>901 Loveridge Road  Pittsburg CA 94565</t>
-  </si>
-  <si>
-    <t>San Joaquin County</t>
-  </si>
-  <si>
-    <t>Stockton Truss LLC</t>
-  </si>
-  <si>
-    <t>4408 E Fremont St  Stockton CA 95215</t>
-  </si>
-  <si>
-    <t>Ventura County</t>
-  </si>
-  <si>
-    <t>Volume Services, Inc. (Sodexo)</t>
-  </si>
-  <si>
-    <t>40 Presidential Drive  Simi Valley CA 93065</t>
-  </si>
-  <si>
-    <t>Stone Brewing Co., LLC - Executive Place</t>
-  </si>
-  <si>
-    <t>2865 Executive Place  Escondido CA 92029</t>
-  </si>
-  <si>
-    <t>Stone Brewing Co., LLC - Harmony Grove</t>
-  </si>
-  <si>
-    <t>2005 Harmony Grove Rd.  Escondido CA 92029</t>
-  </si>
-  <si>
-    <t>Stone Brewing CO., LLC - Citracado Parkway</t>
-  </si>
-  <si>
-    <t>1999 Citracado Parkway  Escondido CA 92029</t>
+    <t>Flying Food Group, LLC</t>
+  </si>
+  <si>
+    <t>50 Adrian Ct  Burlingame CA 94010</t>
+  </si>
+  <si>
+    <t>3250 Patterson Road  Riverbank CA 95367</t>
+  </si>
+  <si>
+    <t>Haas Automation, Inc.</t>
+  </si>
+  <si>
+    <t>2800 Sturgis Road  Oxnard CA 93030</t>
+  </si>
+  <si>
+    <t>Blue Shield of California</t>
+  </si>
+  <si>
+    <t>601 12th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>El Dorado County</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building C)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building B)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95672</t>
+  </si>
+  <si>
+    <t>3840 Kilroy Airport Way  Long Beach CA 90806</t>
+  </si>
+  <si>
+    <t>6300 Canoga Avenue  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>3300 Zinfandel Drive  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>3131 Camino Del Rio, Suite #1300  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>3021 Reynolds Ranch Parkway  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Cellares Corporation</t>
+  </si>
+  <si>
+    <t>1100 Veterans Boulevard  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Cupertino</t>
+  </si>
+  <si>
+    <t>One Apple Park Way  Cupertino CA 95014</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Sunnyvale</t>
+  </si>
+  <si>
+    <t>599 N. Mathilda Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Maude Ave.</t>
+  </si>
+  <si>
+    <t>605 W. Maude Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Jabil Inc.</t>
+  </si>
+  <si>
+    <t>30 Great Oaks Boulevard  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>BFG Supply Co., LLC</t>
+  </si>
+  <si>
+    <t>2552 Shenandoah Way  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>3740 Seaport Boulevard, Suite 10  West Sacramento CA 95691</t>
   </si>
   <si>
     <r>
@@ -1177,7 +1267,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/19/2026</t>
+      <t>07/01/26 to 08/24/2026</t>
     </r>
     <r>
       <rPr>
@@ -1197,7 +1287,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I138.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I156.</t>
     </r>
   </si>
 </sst>
@@ -2363,8 +2453,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I138" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I138" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I156" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I156" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2711,37 +2801,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.90625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>24</v>
       </c>
@@ -2760,18 +2850,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
@@ -2779,34 +2869,34 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>6777</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7770</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2815,25 +2905,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -2853,32 +2943,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I156"/>
+  <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.54296875" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -2907,7 +2997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
@@ -2936,7 +3026,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>55</v>
       </c>
@@ -2965,7 +3055,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>54</v>
       </c>
@@ -2994,7 +3084,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>56</v>
       </c>
@@ -3023,7 +3113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
@@ -3052,7 +3142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
         <v>53</v>
       </c>
@@ -3081,7 +3171,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
         <v>53</v>
       </c>
@@ -3110,7 +3200,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
         <v>57</v>
       </c>
@@ -3139,7 +3229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>55</v>
       </c>
@@ -3168,7 +3258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="28" t="s">
         <v>76</v>
       </c>
@@ -3197,7 +3287,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
         <v>79</v>
       </c>
@@ -3226,7 +3316,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
         <v>82</v>
       </c>
@@ -3255,7 +3345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>53</v>
       </c>
@@ -3284,7 +3374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
         <v>5</v>
       </c>
@@ -3313,7 +3403,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
         <v>54</v>
       </c>
@@ -3342,7 +3432,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
         <v>53</v>
       </c>
@@ -3371,7 +3461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
         <v>53</v>
       </c>
@@ -3400,7 +3490,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
         <v>54</v>
       </c>
@@ -3429,7 +3519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
         <v>79</v>
       </c>
@@ -3458,7 +3548,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
         <v>99</v>
       </c>
@@ -3487,7 +3577,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
         <v>103</v>
       </c>
@@ -3516,7 +3606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="28" t="s">
         <v>53</v>
       </c>
@@ -3545,7 +3635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
         <v>103</v>
       </c>
@@ -3574,7 +3664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
         <v>110</v>
       </c>
@@ -3603,7 +3693,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3722,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="28" t="s">
         <v>5</v>
       </c>
@@ -3661,7 +3751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
         <v>5</v>
       </c>
@@ -3690,7 +3780,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
         <v>5</v>
       </c>
@@ -3719,7 +3809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="28" t="s">
         <v>5</v>
       </c>
@@ -3748,7 +3838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="28" t="s">
         <v>54</v>
       </c>
@@ -3777,7 +3867,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
         <v>103</v>
       </c>
@@ -3806,7 +3896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="28" t="s">
         <v>127</v>
       </c>
@@ -3835,7 +3925,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="28" t="s">
         <v>103</v>
       </c>
@@ -3864,7 +3954,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
         <v>53</v>
       </c>
@@ -3893,7 +3983,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
         <v>135</v>
       </c>
@@ -3922,7 +4012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
         <v>138</v>
       </c>
@@ -3951,7 +4041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
         <v>103</v>
       </c>
@@ -3980,7 +4070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
         <v>76</v>
       </c>
@@ -4009,7 +4099,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
         <v>138</v>
       </c>
@@ -4038,7 +4128,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
         <v>138</v>
       </c>
@@ -4067,7 +4157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="33" t="s">
         <v>149</v>
       </c>
@@ -4096,7 +4186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="33" t="s">
         <v>79</v>
       </c>
@@ -4125,7 +4215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="33" t="s">
         <v>79</v>
       </c>
@@ -4154,7 +4244,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>79</v>
       </c>
@@ -4183,7 +4273,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="33" t="s">
         <v>5</v>
       </c>
@@ -4212,7 +4302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="33" t="s">
         <v>160</v>
       </c>
@@ -4241,7 +4331,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="33" t="s">
         <v>103</v>
       </c>
@@ -4270,7 +4360,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="33" t="s">
         <v>103</v>
       </c>
@@ -4299,7 +4389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>103</v>
       </c>
@@ -4328,7 +4418,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="33" t="s">
         <v>103</v>
       </c>
@@ -4357,7 +4447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="33" t="s">
         <v>171</v>
       </c>
@@ -4386,7 +4476,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="33" t="s">
         <v>171</v>
       </c>
@@ -4415,7 +4505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
         <v>53</v>
       </c>
@@ -4444,7 +4534,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="28" t="s">
         <v>76</v>
       </c>
@@ -4473,7 +4563,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="28" t="s">
         <v>180</v>
       </c>
@@ -4502,7 +4592,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="28" t="s">
         <v>5</v>
       </c>
@@ -4531,7 +4621,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="28" t="s">
         <v>5</v>
       </c>
@@ -4560,7 +4650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="28" t="s">
         <v>53</v>
       </c>
@@ -4589,7 +4679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="28" t="s">
         <v>189</v>
       </c>
@@ -4618,7 +4708,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="28" t="s">
         <v>56</v>
       </c>
@@ -4647,7 +4737,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="28" t="s">
         <v>55</v>
       </c>
@@ -4676,7 +4766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="28" t="s">
         <v>110</v>
       </c>
@@ -4705,7 +4795,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="28" t="s">
         <v>110</v>
       </c>
@@ -4734,7 +4824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="28" t="s">
         <v>199</v>
       </c>
@@ -4763,7 +4853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="28" t="s">
         <v>138</v>
       </c>
@@ -4792,7 +4882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="28" t="s">
         <v>138</v>
       </c>
@@ -4821,7 +4911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
         <v>103</v>
       </c>
@@ -4850,7 +4940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="28" t="s">
         <v>207</v>
       </c>
@@ -4879,7 +4969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="28" t="s">
         <v>171</v>
       </c>
@@ -4908,7 +4998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="28" t="s">
         <v>53</v>
       </c>
@@ -4937,7 +5027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="28" t="s">
         <v>189</v>
       </c>
@@ -4966,7 +5056,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="28" t="s">
         <v>54</v>
       </c>
@@ -4995,7 +5085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="28" t="s">
         <v>216</v>
       </c>
@@ -5024,7 +5114,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="28" t="s">
         <v>56</v>
       </c>
@@ -5053,7 +5143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="28" t="s">
         <v>171</v>
       </c>
@@ -5082,7 +5172,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="28" t="s">
         <v>180</v>
       </c>
@@ -5111,7 +5201,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="28" t="s">
         <v>180</v>
       </c>
@@ -5140,7 +5230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="28" t="s">
         <v>180</v>
       </c>
@@ -5169,7 +5259,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="28" t="s">
         <v>180</v>
       </c>
@@ -5198,7 +5288,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="28" t="s">
         <v>180</v>
       </c>
@@ -5227,7 +5317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="28" t="s">
         <v>55</v>
       </c>
@@ -5256,7 +5346,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="28" t="s">
         <v>53</v>
       </c>
@@ -5285,7 +5375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="28" t="s">
         <v>53</v>
       </c>
@@ -5314,7 +5404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="28" t="s">
         <v>54</v>
       </c>
@@ -5343,7 +5433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="28" t="s">
         <v>54</v>
       </c>
@@ -5372,7 +5462,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="28" t="s">
         <v>79</v>
       </c>
@@ -5401,7 +5491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="28" t="s">
         <v>79</v>
       </c>
@@ -5430,7 +5520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="28" t="s">
         <v>103</v>
       </c>
@@ -5459,7 +5549,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="28" t="s">
         <v>54</v>
       </c>
@@ -5488,7 +5578,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="28" t="s">
         <v>79</v>
       </c>
@@ -5517,7 +5607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="33" t="s">
         <v>5</v>
       </c>
@@ -5546,7 +5636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="33" t="s">
         <v>5</v>
       </c>
@@ -5575,7 +5665,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="33" t="s">
         <v>5</v>
       </c>
@@ -5604,7 +5694,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="33" t="s">
         <v>5</v>
       </c>
@@ -5633,7 +5723,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="33" t="s">
         <v>189</v>
       </c>
@@ -5662,7 +5752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>56</v>
       </c>
@@ -5691,7 +5781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="33" t="s">
         <v>171</v>
       </c>
@@ -5720,7 +5810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="33" t="s">
         <v>260</v>
       </c>
@@ -5749,7 +5839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="33" t="s">
         <v>171</v>
       </c>
@@ -5778,7 +5868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
         <v>5</v>
       </c>
@@ -5807,7 +5897,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
         <v>189</v>
       </c>
@@ -5836,7 +5926,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="28" t="s">
         <v>207</v>
       </c>
@@ -5865,7 +5955,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="28" t="s">
         <v>207</v>
       </c>
@@ -5894,7 +5984,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="28" t="s">
         <v>207</v>
       </c>
@@ -5923,7 +6013,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="28" t="s">
         <v>207</v>
       </c>
@@ -5952,7 +6042,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="28" t="s">
         <v>207</v>
       </c>
@@ -5981,7 +6071,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="28" t="s">
         <v>5</v>
       </c>
@@ -6010,7 +6100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="28" t="s">
         <v>76</v>
       </c>
@@ -6039,7 +6129,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="28" t="s">
         <v>76</v>
       </c>
@@ -6068,7 +6158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="28" t="s">
         <v>76</v>
       </c>
@@ -6097,7 +6187,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
         <v>76</v>
       </c>
@@ -6126,7 +6216,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="28" t="s">
         <v>76</v>
       </c>
@@ -6155,7 +6245,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="28" t="s">
         <v>76</v>
       </c>
@@ -6184,7 +6274,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="28" t="s">
         <v>76</v>
       </c>
@@ -6213,7 +6303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="28" t="s">
         <v>76</v>
       </c>
@@ -6242,7 +6332,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="28" t="s">
         <v>76</v>
       </c>
@@ -6271,7 +6361,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="28" t="s">
         <v>76</v>
       </c>
@@ -6300,7 +6390,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="28" t="s">
         <v>76</v>
       </c>
@@ -6329,7 +6419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="28" t="s">
         <v>76</v>
       </c>
@@ -6358,7 +6448,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="28" t="s">
         <v>76</v>
       </c>
@@ -6387,7 +6477,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="28" t="s">
         <v>76</v>
       </c>
@@ -6416,7 +6506,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="28" t="s">
         <v>76</v>
       </c>
@@ -6445,7 +6535,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="28" t="s">
         <v>76</v>
       </c>
@@ -6474,7 +6564,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="28" t="s">
         <v>76</v>
       </c>
@@ -6503,7 +6593,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="28" t="s">
         <v>57</v>
       </c>
@@ -6532,7 +6622,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="28" t="s">
         <v>57</v>
       </c>
@@ -6561,7 +6651,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="28" t="s">
         <v>5</v>
       </c>
@@ -6590,7 +6680,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="28" t="s">
         <v>5</v>
       </c>
@@ -6619,7 +6709,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="28" t="s">
         <v>5</v>
       </c>
@@ -6648,7 +6738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="28" t="s">
         <v>55</v>
       </c>
@@ -6677,7 +6767,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="28" t="s">
         <v>57</v>
       </c>
@@ -6691,7 +6781,7 @@
         <v>46325</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F133" s="28" t="s">
         <v>6</v>
@@ -6700,15 +6790,15 @@
         <v>2</v>
       </c>
       <c r="H133" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I133" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B134" s="29">
         <v>46252</v>
@@ -6720,7 +6810,7 @@
         <v>46313</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F134" s="28" t="s">
         <v>6</v>
@@ -6729,15 +6819,15 @@
         <v>65</v>
       </c>
       <c r="H134" s="30" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I134" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B135" s="29">
         <v>46251</v>
@@ -6749,7 +6839,7 @@
         <v>46311</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F135" s="28" t="s">
         <v>6</v>
@@ -6758,13 +6848,13 @@
         <v>93</v>
       </c>
       <c r="H135" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I135" s="32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="28" t="s">
         <v>207</v>
       </c>
@@ -6778,7 +6868,7 @@
         <v>46314</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F136" s="28" t="s">
         <v>52</v>
@@ -6787,13 +6877,13 @@
         <v>6</v>
       </c>
       <c r="H136" s="30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I136" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="28" t="s">
         <v>207</v>
       </c>
@@ -6807,7 +6897,7 @@
         <v>46314</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F137" s="28" t="s">
         <v>52</v>
@@ -6816,13 +6906,13 @@
         <v>2</v>
       </c>
       <c r="H137" s="30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I137" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="28" t="s">
         <v>207</v>
       </c>
@@ -6836,7 +6926,7 @@
         <v>46314</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F138" s="28" t="s">
         <v>52</v>
@@ -6845,10 +6935,532 @@
         <v>50</v>
       </c>
       <c r="H138" s="30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I138" s="32" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" s="29">
+        <v>46248</v>
+      </c>
+      <c r="C139" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D139" s="29">
+        <v>46308</v>
+      </c>
+      <c r="E139" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="F139" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G139" s="30">
+        <v>72</v>
+      </c>
+      <c r="H139" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="I139" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" s="29">
+        <v>46246</v>
+      </c>
+      <c r="C140" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D140" s="29">
+        <v>46307</v>
+      </c>
+      <c r="E140" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F140" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G140" s="30">
+        <v>120</v>
+      </c>
+      <c r="H140" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="I140" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B141" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C141" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D141" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E141" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="F141" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="30">
+        <v>73</v>
+      </c>
+      <c r="H141" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="I141" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B142" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C142" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D142" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F142" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="30">
+        <v>25</v>
+      </c>
+      <c r="H142" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="I142" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B143" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C143" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D143" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E143" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="F143" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="30">
+        <v>1</v>
+      </c>
+      <c r="H143" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="I143" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B144" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C144" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D144" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="30">
+        <v>12</v>
+      </c>
+      <c r="H144" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="I144" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C145" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D145" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E145" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" s="30">
+        <v>8</v>
+      </c>
+      <c r="H145" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="I145" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C146" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D146" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G146" s="30">
+        <v>3</v>
+      </c>
+      <c r="H146" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="I146" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B147" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C147" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D147" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E147" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="30">
+        <v>5</v>
+      </c>
+      <c r="H147" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="I147" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B148" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C148" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D148" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="30">
+        <v>4</v>
+      </c>
+      <c r="H148" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="I148" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C149" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D149" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" s="30">
+        <v>2</v>
+      </c>
+      <c r="H149" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="I149" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B150" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C150" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D150" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" s="30">
+        <v>100</v>
+      </c>
+      <c r="H150" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="I150" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B151" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C151" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D151" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E151" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" s="30">
+        <v>79</v>
+      </c>
+      <c r="H151" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="I151" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B152" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C152" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D152" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E152" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="F152" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" s="30">
+        <v>28</v>
+      </c>
+      <c r="H152" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="I152" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B153" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C153" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D153" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E153" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="F153" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G153" s="30">
+        <v>40</v>
+      </c>
+      <c r="H153" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="I153" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B154" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C154" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D154" s="29">
+        <v>46349</v>
+      </c>
+      <c r="E154" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="F154" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G154" s="30">
+        <v>382</v>
+      </c>
+      <c r="H154" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="I154" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B155" s="29">
+        <v>46258</v>
+      </c>
+      <c r="C155" s="29">
+        <v>46258</v>
+      </c>
+      <c r="D155" s="29">
+        <v>46320</v>
+      </c>
+      <c r="E155" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G155" s="30">
+        <v>37</v>
+      </c>
+      <c r="H155" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="I155" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B156" s="29">
+        <v>46258</v>
+      </c>
+      <c r="C156" s="29">
+        <v>46258</v>
+      </c>
+      <c r="D156" s="29">
+        <v>46320</v>
+      </c>
+      <c r="E156" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="F156" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" s="30">
+        <v>2</v>
+      </c>
+      <c r="H156" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="I156" s="32" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -6865,7 +7477,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I138</xm:sqref>
+          <xm:sqref>I3:I156</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6876,18 +7488,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="95" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
@@ -6895,7 +7507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>17</v>
       </c>
@@ -6904,7 +7516,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
@@ -6913,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>10</v>
       </c>
@@ -6922,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
@@ -6931,7 +7543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>12</v>
       </c>
@@ -6940,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
@@ -6949,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>14</v>
       </c>
@@ -6972,25 +7584,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -7016,7 +7628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -7053,117 +7665,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -7401,7 +8013,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{500E637C-873A-43B6-8715-BFB319569621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B82B9673-ED21-4933-9A9C-773CB2F4FD2E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7420,7 +8032,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FEEF22E-DAEA-47B0-88B1-91EB0D24CA24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCADA38-B649-43B5-8987-30F05437E106}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -7428,18 +8040,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F711838-DD4B-4223-BB8C-8018EF2910A0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BE6D488-2A3F-46E6-B9DE-C01E1051C417}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
